--- a/05_Figures/F05_classification/c_data/results.xlsx
+++ b/05_Figures/F05_classification/c_data/results.xlsx
@@ -495,7 +495,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -530,10 +530,10 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -544,15 +544,9 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0630357142857143</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.191926228301501</v>
-      </c>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -571,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -606,10 +600,10 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -620,15 +614,9 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.063125</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.194785083577329</v>
-      </c>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -647,19 +635,19 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.125</v>
+        <v>0.196428571428571</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.369995498067507</v>
+        <v>0.465263732604026</v>
       </c>
       <c r="K6"/>
       <c r="L6"/>
@@ -682,29 +670,23 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.125</v>
+        <v>0.196428571428571</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.369995498067507</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.388059701492537</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.130357142857143</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.184659326226387</v>
-      </c>
+        <v>0.465263732604026</v>
+      </c>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -723,19 +705,19 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.723214285714286</v>
+        <v>0.455357142857143</v>
       </c>
       <c r="I8" t="n">
-        <v>0.433140603759377</v>
+        <v>0.16803638821707</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.742677897497216</v>
       </c>
       <c r="K8"/>
       <c r="L8"/>
@@ -758,29 +740,23 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.723214285714286</v>
+        <v>0.455357142857143</v>
       </c>
       <c r="I9" t="n">
-        <v>0.433140603759377</v>
+        <v>0.16803638821707</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.149253731343284</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.509866071428571</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.181857765842163</v>
-      </c>
+        <v>0.742677897497216</v>
+      </c>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -799,19 +775,19 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.553571428571429</v>
+        <v>0.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.233616372813172</v>
+        <v>0.176509421932077</v>
       </c>
       <c r="J10" t="n">
-        <v>0.873526484329685</v>
+        <v>0.823490578067923</v>
       </c>
       <c r="K10"/>
       <c r="L10"/>
@@ -834,29 +810,23 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.553571428571429</v>
+        <v>0.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0.233616372813172</v>
+        <v>0.176509421932077</v>
       </c>
       <c r="J11" t="n">
-        <v>0.873526484329685</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.228855721393035</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.383303571428571</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.208293502413979</v>
-      </c>
+        <v>0.823490578067923</v>
+      </c>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -875,7 +845,7 @@
         <v>15</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -910,10 +880,10 @@
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -924,15 +894,9 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.02875</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.126911974683316</v>
-      </c>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -951,19 +915,19 @@
         <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.410714285714286</v>
+        <v>0.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0862334739795216</v>
+        <v>0.176780012174383</v>
       </c>
       <c r="J14" t="n">
-        <v>0.73519509744905</v>
+        <v>0.823219987825617</v>
       </c>
       <c r="K14"/>
       <c r="L14"/>
@@ -986,29 +950,23 @@
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.410714285714286</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0862334739795216</v>
+        <v>0.176780012174383</v>
       </c>
       <c r="J15" t="n">
-        <v>0.73519509744905</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.487562189054726</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.405089285714286</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.206870825875968</v>
-      </c>
+        <v>0.823219987825617</v>
+      </c>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -1027,19 +985,19 @@
         <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.357142857142857</v>
+        <v>0.482142857142857</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0360958014326752</v>
+        <v>0.153730967094126</v>
       </c>
       <c r="J16" t="n">
-        <v>0.678189912853039</v>
+        <v>0.810554747191589</v>
       </c>
       <c r="K16"/>
       <c r="L16"/>
@@ -1062,29 +1020,23 @@
         <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.357142857142857</v>
+        <v>0.482142857142857</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0360958014326752</v>
+        <v>0.153730967094126</v>
       </c>
       <c r="J17" t="n">
-        <v>0.678189912853039</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.398009950248756</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.295625</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.26147700328391</v>
-      </c>
+        <v>0.810554747191589</v>
+      </c>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -1103,7 +1055,7 @@
         <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1138,10 +1090,10 @@
         <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1152,15 +1104,9 @@
       <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.0589285714285714</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.173048104873612</v>
-      </c>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -1179,7 +1125,7 @@
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1214,10 +1160,10 @@
         <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1228,15 +1174,9 @@
       <c r="J21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.0573214285714286</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.177884446682823</v>
-      </c>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -1255,7 +1195,7 @@
         <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1290,10 +1230,10 @@
         <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1304,15 +1244,9 @@
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.190357142857143</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.24348263060434</v>
-      </c>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
@@ -1331,19 +1265,19 @@
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.633928571428571</v>
+        <v>0.732142857142857</v>
       </c>
       <c r="I24" t="n">
-        <v>0.351651393887878</v>
+        <v>0.47370676820766</v>
       </c>
       <c r="J24" t="n">
-        <v>0.916205748969265</v>
+        <v>0.990578946078055</v>
       </c>
       <c r="K24"/>
       <c r="L24"/>
@@ -1366,29 +1300,23 @@
         <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.633928571428571</v>
+        <v>0.732142857142857</v>
       </c>
       <c r="I25" t="n">
-        <v>0.351651393887878</v>
+        <v>0.47370676820766</v>
       </c>
       <c r="J25" t="n">
-        <v>0.916205748969265</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.263681592039801</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.5153125</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.187873260022492</v>
-      </c>
+        <v>0.990578946078055</v>
+      </c>
+      <c r="K25"/>
+      <c r="L25"/>
+      <c r="M25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
@@ -1407,19 +1335,19 @@
         <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.0110832093203027</v>
       </c>
       <c r="J26" t="n">
-        <v>0.468052601982907</v>
+        <v>0.560345362108269</v>
       </c>
       <c r="K26"/>
       <c r="L26"/>
@@ -1442,29 +1370,23 @@
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.0110832093203027</v>
       </c>
       <c r="J27" t="n">
-        <v>0.468052601982907</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.756218905472637</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.392589285714286</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.224984741076044</v>
-      </c>
+        <v>0.560345362108269</v>
+      </c>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
@@ -1483,7 +1405,7 @@
         <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1518,10 +1440,10 @@
         <v>15</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1532,15 +1454,9 @@
       <c r="J29" t="n">
         <v>0</v>
       </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.0415178571428571</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.157668733367119</v>
-      </c>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
@@ -1559,19 +1475,19 @@
         <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.196428571428571</v>
+        <v>0.303571428571429</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.0164791596570672</v>
       </c>
       <c r="J30" t="n">
-        <v>0.432944132868089</v>
+        <v>0.59066369748579</v>
       </c>
       <c r="K30"/>
       <c r="L30"/>
@@ -1594,29 +1510,23 @@
         <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.196428571428571</v>
+        <v>0.303571428571429</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.0164791596570672</v>
       </c>
       <c r="J31" t="n">
-        <v>0.432944132868089</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.840796019900497</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.430089285714286</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.22882855173496</v>
-      </c>
+        <v>0.59066369748579</v>
+      </c>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
@@ -1635,19 +1545,19 @@
         <v>15</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.178571428571429</v>
+        <v>0.125</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.426642799354743</v>
+        <v>0.372482825776728</v>
       </c>
       <c r="K32"/>
       <c r="L32"/>
@@ -1670,29 +1580,23 @@
         <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G33" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.178571428571429</v>
+        <v>0.125</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.426642799354743</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.587064676616915</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.296607142857143</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.26405102742189</v>
-      </c>
+        <v>0.372482825776728</v>
+      </c>
+      <c r="K33"/>
+      <c r="L33"/>
+      <c r="M33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
@@ -1711,7 +1615,7 @@
         <v>15</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1746,10 +1650,10 @@
         <v>15</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G35" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1760,15 +1664,9 @@
       <c r="J35" t="n">
         <v>0</v>
       </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.0511607142857143</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.16743521895316</v>
-      </c>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
@@ -1787,7 +1685,7 @@
         <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1822,10 +1720,10 @@
         <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G37" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1836,15 +1734,9 @@
       <c r="J37" t="n">
         <v>0</v>
       </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.0519642857142857</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.176887157549663</v>
-      </c>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
@@ -1863,19 +1755,19 @@
         <v>15</v>
       </c>
       <c r="F38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.369995498067507</v>
+        <v>0</v>
       </c>
       <c r="K38"/>
       <c r="L38"/>
@@ -1898,29 +1790,23 @@
         <v>15</v>
       </c>
       <c r="F39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G39" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.369995498067507</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.437810945273632</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.149464285714286</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.19799520465546</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
@@ -1939,19 +1825,19 @@
         <v>15</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.267857142857143</v>
+        <v>0.321428571428571</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0262179060489883</v>
+        <v>0.0892691021668111</v>
       </c>
       <c r="J40" t="n">
-        <v>0.509496379665297</v>
+        <v>0.553588040690332</v>
       </c>
       <c r="K40"/>
       <c r="L40"/>
@@ -1974,29 +1860,23 @@
         <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G41" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.267857142857143</v>
+        <v>0.321428571428571</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0262179060489883</v>
+        <v>0.0892691021668111</v>
       </c>
       <c r="J41" t="n">
-        <v>0.509496379665297</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.885572139303483</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.515625</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.20398164846116</v>
-      </c>
+        <v>0.553588040690332</v>
+      </c>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
@@ -2015,19 +1895,19 @@
         <v>15</v>
       </c>
       <c r="F42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.428571428571429</v>
+        <v>0.339285714285714</v>
       </c>
       <c r="I42" t="n">
-        <v>0.105622257708171</v>
+        <v>0.0403486265399839</v>
       </c>
       <c r="J42" t="n">
-        <v>0.751520599434686</v>
+        <v>0.638222802031445</v>
       </c>
       <c r="K42"/>
       <c r="L42"/>
@@ -2050,29 +1930,23 @@
         <v>15</v>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G43" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.428571428571429</v>
+        <v>0.339285714285714</v>
       </c>
       <c r="I43" t="n">
-        <v>0.105622257708171</v>
+        <v>0.0403486265399839</v>
       </c>
       <c r="J43" t="n">
-        <v>0.751520599434686</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.398009950248756</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.366160714285714</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.219625657378727</v>
-      </c>
+        <v>0.638222802031445</v>
+      </c>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
@@ -2091,7 +1965,7 @@
         <v>15</v>
       </c>
       <c r="F44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2126,10 +2000,10 @@
         <v>15</v>
       </c>
       <c r="F45" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G45" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2140,15 +2014,9 @@
       <c r="J45" t="n">
         <v>0</v>
       </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.023125</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.112281041550031</v>
-      </c>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
@@ -2167,7 +2035,7 @@
         <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2176,10 +2044,10 @@
         <v>0.321428571428571</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0229797039788519</v>
+        <v>0.0233708560046663</v>
       </c>
       <c r="J46" t="n">
-        <v>0.619877438878291</v>
+        <v>0.619486286852477</v>
       </c>
       <c r="K46"/>
       <c r="L46"/>
@@ -2202,29 +2070,23 @@
         <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0.321428571428571</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0229797039788519</v>
+        <v>0.0233708560046663</v>
       </c>
       <c r="J47" t="n">
-        <v>0.619877438878291</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.646766169154229</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.414375</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.211851282116214</v>
-      </c>
+        <v>0.619486286852477</v>
+      </c>
+      <c r="K47"/>
+      <c r="L47"/>
+      <c r="M47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
@@ -2243,19 +2105,19 @@
         <v>15</v>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.107142857142857</v>
+        <v>0.0892857142857143</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.276550487641665</v>
+        <v>0.271628188926489</v>
       </c>
       <c r="K48"/>
       <c r="L48"/>
@@ -2278,29 +2140,23 @@
         <v>15</v>
       </c>
       <c r="F49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.107142857142857</v>
+        <v>0.0892857142857143</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.276550487641665</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.810945273631841</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.297410714285714</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.234170951326558</v>
-      </c>
+        <v>0.271628188926489</v>
+      </c>
+      <c r="K49"/>
+      <c r="L49"/>
+      <c r="M49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
@@ -2319,7 +2175,7 @@
         <v>15</v>
       </c>
       <c r="F50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2354,10 +2210,10 @@
         <v>15</v>
       </c>
       <c r="F51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G51" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2368,15 +2224,9 @@
       <c r="J51" t="n">
         <v>0</v>
       </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.0495535714285714</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.167442492198123</v>
-      </c>
+      <c r="K51"/>
+      <c r="L51"/>
+      <c r="M51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
@@ -2395,7 +2245,7 @@
         <v>15</v>
       </c>
       <c r="F52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2430,10 +2280,10 @@
         <v>15</v>
       </c>
       <c r="F53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G53" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2444,15 +2294,9 @@
       <c r="J53" t="n">
         <v>0</v>
       </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0.0554464285714286</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0.180485057842753</v>
-      </c>
+      <c r="K53"/>
+      <c r="L53"/>
+      <c r="M53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
@@ -2471,19 +2315,19 @@
         <v>15</v>
       </c>
       <c r="F54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.125</v>
+        <v>0.0892857142857143</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.312079431647071</v>
+        <v>0.270021615983094</v>
       </c>
       <c r="K54"/>
       <c r="L54"/>
@@ -2506,29 +2350,23 @@
         <v>15</v>
       </c>
       <c r="F55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G55" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.125</v>
+        <v>0.0892857142857143</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.312079431647071</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.3681592039801</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0.121607142857143</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.188212376933318</v>
-      </c>
+        <v>0.270021615983094</v>
+      </c>
+      <c r="K55"/>
+      <c r="L55"/>
+      <c r="M55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
@@ -2547,19 +2385,19 @@
         <v>15</v>
       </c>
       <c r="F56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.446428571428571</v>
+        <v>0.383928571428571</v>
       </c>
       <c r="I56" t="n">
-        <v>0.164797900113296</v>
+        <v>0.105579146148296</v>
       </c>
       <c r="J56" t="n">
-        <v>0.728059242743846</v>
+        <v>0.662277996708847</v>
       </c>
       <c r="K56"/>
       <c r="L56"/>
@@ -2582,29 +2420,23 @@
         <v>15</v>
       </c>
       <c r="F57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G57" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.446428571428571</v>
+        <v>0.383928571428571</v>
       </c>
       <c r="I57" t="n">
-        <v>0.164797900113296</v>
+        <v>0.105579146148296</v>
       </c>
       <c r="J57" t="n">
-        <v>0.728059242743846</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.616915422885572</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0.510982142857143</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.177386841729617</v>
-      </c>
+        <v>0.662277996708847</v>
+      </c>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
@@ -2623,19 +2455,19 @@
         <v>15</v>
       </c>
       <c r="F58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.410714285714286</v>
+        <v>0.321428571428571</v>
       </c>
       <c r="I58" t="n">
-        <v>0.077891616708458</v>
+        <v>0.0129838110615196</v>
       </c>
       <c r="J58" t="n">
-        <v>0.743536954720113</v>
+        <v>0.629873331795623</v>
       </c>
       <c r="K58"/>
       <c r="L58"/>
@@ -2658,29 +2490,23 @@
         <v>15</v>
       </c>
       <c r="F59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G59" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.410714285714286</v>
+        <v>0.321428571428571</v>
       </c>
       <c r="I59" t="n">
-        <v>0.077891616708458</v>
+        <v>0.0129838110615196</v>
       </c>
       <c r="J59" t="n">
-        <v>0.743536954720113</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0.383084577114428</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0.343571428571429</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.218023749740075</v>
-      </c>
+        <v>0.629873331795623</v>
+      </c>
+      <c r="K59"/>
+      <c r="L59"/>
+      <c r="M59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
@@ -2699,7 +2525,7 @@
         <v>15</v>
       </c>
       <c r="F60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2734,10 +2560,10 @@
         <v>15</v>
       </c>
       <c r="F61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2748,15 +2574,9 @@
       <c r="J61" t="n">
         <v>0</v>
       </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0.0271428571428571</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.136030820646376</v>
-      </c>
+      <c r="K61"/>
+      <c r="L61"/>
+      <c r="M61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
@@ -2775,19 +2595,19 @@
         <v>15</v>
       </c>
       <c r="F62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.464285714285714</v>
+        <v>0.446428571428571</v>
       </c>
       <c r="I62" t="n">
-        <v>0.112215014215032</v>
+        <v>0.116333642465224</v>
       </c>
       <c r="J62" t="n">
-        <v>0.816356414356396</v>
+        <v>0.776523500391919</v>
       </c>
       <c r="K62"/>
       <c r="L62"/>
@@ -2810,29 +2630,23 @@
         <v>15</v>
       </c>
       <c r="F63" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G63" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.464285714285714</v>
+        <v>0.446428571428571</v>
       </c>
       <c r="I63" t="n">
-        <v>0.112215014215032</v>
+        <v>0.116333642465224</v>
       </c>
       <c r="J63" t="n">
-        <v>0.816356414356396</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0.318407960199005</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0.357589285714286</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0.229420627702577</v>
-      </c>
+        <v>0.776523500391919</v>
+      </c>
+      <c r="K63"/>
+      <c r="L63"/>
+      <c r="M63"/>
     </row>
     <row r="64">
       <c r="A64" t="s">
@@ -2851,19 +2665,19 @@
         <v>15</v>
       </c>
       <c r="F64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.285714285714286</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.594914576326202</v>
+        <v>0.422851997791436</v>
       </c>
       <c r="K64"/>
       <c r="L64"/>
@@ -2886,29 +2700,23 @@
         <v>15</v>
       </c>
       <c r="F65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G65" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.285714285714286</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.594914576326202</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0.393034825870647</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0.273125</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0.254187556547724</v>
-      </c>
+        <v>0.422851997791436</v>
+      </c>
+      <c r="K65"/>
+      <c r="L65"/>
+      <c r="M65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
@@ -2927,7 +2735,7 @@
         <v>14</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2962,10 +2770,10 @@
         <v>14</v>
       </c>
       <c r="F67" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G67" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2976,15 +2784,9 @@
       <c r="J67" t="n">
         <v>0</v>
       </c>
-      <c r="K67" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0.0515625</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0.167044921220645</v>
-      </c>
+      <c r="K67"/>
+      <c r="L67"/>
+      <c r="M67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
@@ -3003,7 +2805,7 @@
         <v>14</v>
       </c>
       <c r="F68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -3038,10 +2840,10 @@
         <v>14</v>
       </c>
       <c r="F69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G69" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3052,15 +2854,9 @@
       <c r="J69" t="n">
         <v>0</v>
       </c>
-      <c r="K69" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0.0492708333333333</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0.174631420451172</v>
-      </c>
+      <c r="K69"/>
+      <c r="L69"/>
+      <c r="M69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
@@ -3079,7 +2875,7 @@
         <v>14</v>
       </c>
       <c r="F70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -3114,10 +2910,10 @@
         <v>14</v>
       </c>
       <c r="F71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G71" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3128,15 +2924,9 @@
       <c r="J71" t="n">
         <v>0</v>
       </c>
-      <c r="K71" t="n">
-        <v>1</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0.108958333333333</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0.185008219406345</v>
-      </c>
+      <c r="K71"/>
+      <c r="L71"/>
+      <c r="M71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
@@ -3155,19 +2945,19 @@
         <v>14</v>
       </c>
       <c r="F72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.208333333333333</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>0.080601420264518</v>
       </c>
       <c r="J72" t="n">
-        <v>0.437245657092439</v>
+        <v>0.627731913068815</v>
       </c>
       <c r="K72"/>
       <c r="L72"/>
@@ -3190,29 +2980,23 @@
         <v>14</v>
       </c>
       <c r="F73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G73" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.208333333333333</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>0.080601420264518</v>
       </c>
       <c r="J73" t="n">
-        <v>0.437245657092439</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0.950248756218905</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0.51703125</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0.2174291037597</v>
-      </c>
+        <v>0.627731913068815</v>
+      </c>
+      <c r="K73"/>
+      <c r="L73"/>
+      <c r="M73"/>
     </row>
     <row r="74">
       <c r="A74" t="s">
@@ -3231,19 +3015,19 @@
         <v>14</v>
       </c>
       <c r="F74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.458333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="I74" t="n">
-        <v>0.101027399641709</v>
+        <v>0.0840815847492619</v>
       </c>
       <c r="J74" t="n">
-        <v>0.815639267024957</v>
+        <v>0.790918415250738</v>
       </c>
       <c r="K74"/>
       <c r="L74"/>
@@ -3266,29 +3050,23 @@
         <v>14</v>
       </c>
       <c r="F75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G75" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.458333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="I75" t="n">
-        <v>0.101027399641709</v>
+        <v>0.0840815847492619</v>
       </c>
       <c r="J75" t="n">
-        <v>0.815639267024957</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0.258706467661692</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0.321666666666667</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0.203949265513279</v>
-      </c>
+        <v>0.790918415250738</v>
+      </c>
+      <c r="K75"/>
+      <c r="L75"/>
+      <c r="M75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
@@ -3307,7 +3085,7 @@
         <v>14</v>
       </c>
       <c r="F76" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3342,10 +3120,10 @@
         <v>14</v>
       </c>
       <c r="F77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3356,15 +3134,9 @@
       <c r="J77" t="n">
         <v>0</v>
       </c>
-      <c r="K77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0.0319791666666667</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0.13292962430867</v>
-      </c>
+      <c r="K77"/>
+      <c r="L77"/>
+      <c r="M77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
@@ -3383,19 +3155,19 @@
         <v>14</v>
       </c>
       <c r="F78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.291666666666667</v>
+        <v>0.270833333333333</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0.607351466771162</v>
+        <v>0.580269348833198</v>
       </c>
       <c r="K78"/>
       <c r="L78"/>
@@ -3418,29 +3190,23 @@
         <v>14</v>
       </c>
       <c r="F79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>0.291666666666667</v>
+        <v>0.270833333333333</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0.607351466771162</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0.671641791044776</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0.366979166666667</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0.208078544994611</v>
-      </c>
+        <v>0.580269348833198</v>
+      </c>
+      <c r="K79"/>
+      <c r="L79"/>
+      <c r="M79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
@@ -3459,19 +3225,19 @@
         <v>14</v>
       </c>
       <c r="F80" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0.341065720072343</v>
+        <v>0.537572724427035</v>
       </c>
       <c r="K80"/>
       <c r="L80"/>
@@ -3494,29 +3260,23 @@
         <v>14</v>
       </c>
       <c r="F81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G81" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0.341065720072343</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0.686567164179104</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0.309791666666667</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0.264805438701167</v>
-      </c>
+        <v>0.537572724427035</v>
+      </c>
+      <c r="K81"/>
+      <c r="L81"/>
+      <c r="M81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
@@ -3535,7 +3295,7 @@
         <v>14</v>
       </c>
       <c r="F82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3570,10 +3330,10 @@
         <v>14</v>
       </c>
       <c r="F83" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G83" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3584,15 +3344,9 @@
       <c r="J83" t="n">
         <v>0</v>
       </c>
-      <c r="K83" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0.078125</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0.199277095077576</v>
-      </c>
+      <c r="K83"/>
+      <c r="L83"/>
+      <c r="M83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
@@ -3611,7 +3365,7 @@
         <v>14</v>
       </c>
       <c r="F84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3646,10 +3400,10 @@
         <v>14</v>
       </c>
       <c r="F85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G85" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3660,15 +3414,9 @@
       <c r="J85" t="n">
         <v>0</v>
       </c>
-      <c r="K85" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0.069375</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0.187797665265799</v>
-      </c>
+      <c r="K85"/>
+      <c r="L85"/>
+      <c r="M85"/>
     </row>
     <row r="86">
       <c r="A86" t="s">
@@ -3687,7 +3435,7 @@
         <v>14</v>
       </c>
       <c r="F86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3722,10 +3470,10 @@
         <v>14</v>
       </c>
       <c r="F87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G87" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3736,15 +3484,9 @@
       <c r="J87" t="n">
         <v>0</v>
       </c>
-      <c r="K87" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0.14125</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0.211266619676689</v>
-      </c>
+      <c r="K87"/>
+      <c r="L87"/>
+      <c r="M87"/>
     </row>
     <row r="88">
       <c r="A88" t="s">
@@ -3763,19 +3505,19 @@
         <v>14</v>
       </c>
       <c r="F88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.270833333333333</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0282805233732971</v>
+        <v>0.356526486308224</v>
       </c>
       <c r="J88" t="n">
-        <v>0.51338614329337</v>
+        <v>0.935140180358442</v>
       </c>
       <c r="K88"/>
       <c r="L88"/>
@@ -3798,29 +3540,23 @@
         <v>14</v>
       </c>
       <c r="F89" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.270833333333333</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0282805233732971</v>
+        <v>0.356526486308224</v>
       </c>
       <c r="J89" t="n">
-        <v>0.51338614329337</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0.895522388059702</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0.525416666666667</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0.213298353333767</v>
-      </c>
+        <v>0.935140180358442</v>
+      </c>
+      <c r="K89"/>
+      <c r="L89"/>
+      <c r="M89"/>
     </row>
     <row r="90">
       <c r="A90" t="s">
@@ -3839,19 +3575,19 @@
         <v>14</v>
       </c>
       <c r="F90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1875</v>
+        <v>0.104166666666667</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0.456411092588118</v>
+        <v>0.285991235629427</v>
       </c>
       <c r="K90"/>
       <c r="L90"/>
@@ -3874,29 +3610,23 @@
         <v>14</v>
       </c>
       <c r="F91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G91" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1875</v>
+        <v>0.104166666666667</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0.456411092588118</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0.72636815920398</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0.342604166666667</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0.208570818369027</v>
-      </c>
+        <v>0.285991235629427</v>
+      </c>
+      <c r="K91"/>
+      <c r="L91"/>
+      <c r="M91"/>
     </row>
     <row r="92">
       <c r="A92" t="s">
@@ -3915,7 +3645,7 @@
         <v>14</v>
       </c>
       <c r="F92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3950,10 +3680,10 @@
         <v>14</v>
       </c>
       <c r="F93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G93" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3964,15 +3694,9 @@
       <c r="J93" t="n">
         <v>0</v>
       </c>
-      <c r="K93" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0.0398958333333333</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0.163346022511147</v>
-      </c>
+      <c r="K93"/>
+      <c r="L93"/>
+      <c r="M93"/>
     </row>
     <row r="94">
       <c r="A94" t="s">
@@ -3991,19 +3715,19 @@
         <v>14</v>
       </c>
       <c r="F94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.270833333333333</v>
+        <v>0.229166666666667</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0.60025312738578</v>
+        <v>0.526992708579932</v>
       </c>
       <c r="K94"/>
       <c r="L94"/>
@@ -4026,29 +3750,23 @@
         <v>14</v>
       </c>
       <c r="F95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G95" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0.270833333333333</v>
+        <v>0.229166666666667</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0.60025312738578</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0.736318407960199</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0.415104166666667</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0.228761228645274</v>
-      </c>
+        <v>0.526992708579932</v>
+      </c>
+      <c r="K95"/>
+      <c r="L95"/>
+      <c r="M95"/>
     </row>
     <row r="96">
       <c r="A96" t="s">
@@ -4067,19 +3785,19 @@
         <v>14</v>
       </c>
       <c r="F96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0.270833333333333</v>
+        <v>0.104166666666667</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0.58057709233591</v>
+        <v>0.312372804231433</v>
       </c>
       <c r="K96"/>
       <c r="L96"/>
@@ -4102,29 +3820,23 @@
         <v>14</v>
       </c>
       <c r="F97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G97" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>0.270833333333333</v>
+        <v>0.104166666666667</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0.58057709233591</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0.417910447761194</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0.3065625</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0.280741618978883</v>
-      </c>
+        <v>0.312372804231433</v>
+      </c>
+      <c r="K97"/>
+      <c r="L97"/>
+      <c r="M97"/>
     </row>
     <row r="98">
       <c r="A98" t="s">
@@ -4143,7 +3855,7 @@
         <v>14</v>
       </c>
       <c r="F98" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -4178,10 +3890,10 @@
         <v>14</v>
       </c>
       <c r="F99" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G99" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4192,15 +3904,9 @@
       <c r="J99" t="n">
         <v>0</v>
       </c>
-      <c r="K99" t="n">
-        <v>1</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0.205455415343636</v>
-      </c>
+      <c r="K99"/>
+      <c r="L99"/>
+      <c r="M99"/>
     </row>
     <row r="100">
       <c r="A100" t="s">
@@ -4219,7 +3925,7 @@
         <v>14</v>
       </c>
       <c r="F100" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4254,10 +3960,10 @@
         <v>14</v>
       </c>
       <c r="F101" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G101" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -4268,15 +3974,9 @@
       <c r="J101" t="n">
         <v>0</v>
       </c>
-      <c r="K101" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0.0780208333333333</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0.210623897696129</v>
-      </c>
+      <c r="K101"/>
+      <c r="L101"/>
+      <c r="M101"/>
     </row>
     <row r="102">
       <c r="A102" t="s">
@@ -4295,19 +3995,19 @@
         <v>14</v>
       </c>
       <c r="F102" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0.404158501418271</v>
+        <v>0</v>
       </c>
       <c r="K102"/>
       <c r="L102"/>
@@ -4330,29 +4030,23 @@
         <v>14</v>
       </c>
       <c r="F103" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G103" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0.404158501418271</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0.348258706467662</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0.164375</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0.21942610082072</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K103"/>
+      <c r="L103"/>
+      <c r="M103"/>
     </row>
     <row r="104">
       <c r="A104" t="s">
@@ -4371,19 +4065,19 @@
         <v>14</v>
       </c>
       <c r="F104" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>0.229166666666667</v>
+        <v>0.1875</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0.48833526969636</v>
+        <v>0.430739235294357</v>
       </c>
       <c r="K104"/>
       <c r="L104"/>
@@ -4406,29 +4100,23 @@
         <v>14</v>
       </c>
       <c r="F105" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G105" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0.229166666666667</v>
+        <v>0.1875</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0.48833526969636</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0.651741293532338</v>
-      </c>
-      <c r="L105" t="n">
-        <v>0.3359375</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0.211388171579236</v>
-      </c>
+        <v>0.430739235294357</v>
+      </c>
+      <c r="K105"/>
+      <c r="L105"/>
+      <c r="M105"/>
     </row>
     <row r="106">
       <c r="A106" t="s">
@@ -4447,7 +4135,7 @@
         <v>14</v>
       </c>
       <c r="F106" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4482,10 +4170,10 @@
         <v>14</v>
       </c>
       <c r="F107" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G107" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -4496,15 +4184,9 @@
       <c r="J107" t="n">
         <v>0</v>
       </c>
-      <c r="K107" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0.00322916666666666</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0.025071218700313</v>
-      </c>
+      <c r="K107"/>
+      <c r="L107"/>
+      <c r="M107"/>
     </row>
     <row r="108">
       <c r="A108" t="s">
@@ -4523,19 +4205,19 @@
         <v>14</v>
       </c>
       <c r="F108" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>0.416666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0879707139504487</v>
+        <v>0.0104865302211663</v>
       </c>
       <c r="J108" t="n">
-        <v>0.745362619382885</v>
+        <v>0.6561801364455</v>
       </c>
       <c r="K108"/>
       <c r="L108"/>
@@ -4558,29 +4240,23 @@
         <v>14</v>
       </c>
       <c r="F109" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G109" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>0.416666666666667</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0879707139504487</v>
+        <v>0.0104865302211663</v>
       </c>
       <c r="J109" t="n">
-        <v>0.745362619382885</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0.487562189054726</v>
-      </c>
-      <c r="L109" t="n">
-        <v>0.418958333333333</v>
-      </c>
-      <c r="M109" t="n">
-        <v>0.220160414810613</v>
-      </c>
+        <v>0.6561801364455</v>
+      </c>
+      <c r="K109"/>
+      <c r="L109"/>
+      <c r="M109"/>
     </row>
     <row r="110">
       <c r="A110" t="s">
@@ -4599,19 +4275,19 @@
         <v>14</v>
       </c>
       <c r="F110" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>0.104166666666667</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>0.31689955374757</v>
       </c>
       <c r="K110"/>
       <c r="L110"/>
@@ -4634,29 +4310,23 @@
         <v>14</v>
       </c>
       <c r="F111" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G111" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>0.104166666666667</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" t="n">
-        <v>0.343854166666667</v>
-      </c>
-      <c r="M111" t="n">
-        <v>0.264200917434386</v>
-      </c>
+        <v>0.31689955374757</v>
+      </c>
+      <c r="K111"/>
+      <c r="L111"/>
+      <c r="M111"/>
     </row>
     <row r="112">
       <c r="A112" t="s">
@@ -4713,7 +4383,7 @@
         <v>79</v>
       </c>
       <c r="G113" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
         <v>0.142857142857143</v>
@@ -4724,15 +4394,9 @@
       <c r="J113" t="n">
         <v>0.422851997791436</v>
       </c>
-      <c r="K113" t="n">
-        <v>0.199004975124378</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0.105982142857143</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0.225962638790841</v>
-      </c>
+      <c r="K113"/>
+      <c r="L113"/>
+      <c r="M113"/>
     </row>
     <row r="114">
       <c r="A114" t="s">
@@ -4789,7 +4453,7 @@
         <v>79</v>
       </c>
       <c r="G115" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
         <v>0.321428571428571</v>
@@ -4800,15 +4464,9 @@
       <c r="J115" t="n">
         <v>0.647612706214414</v>
       </c>
-      <c r="K115" t="n">
-        <v>0.169154228855721</v>
-      </c>
-      <c r="L115" t="n">
-        <v>0.116071428571429</v>
-      </c>
-      <c r="M115" t="n">
-        <v>0.252519099882679</v>
-      </c>
+      <c r="K115"/>
+      <c r="L115"/>
+      <c r="M115"/>
     </row>
     <row r="116">
       <c r="A116" t="s">
@@ -4865,7 +4523,7 @@
         <v>79</v>
       </c>
       <c r="G117" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
         <v>0.125</v>
@@ -4876,15 +4534,9 @@
       <c r="J117" t="n">
         <v>0.372482825776728</v>
       </c>
-      <c r="K117" t="n">
-        <v>0.572139303482587</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0.213839285714286</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0.221206421660859</v>
-      </c>
+      <c r="K117"/>
+      <c r="L117"/>
+      <c r="M117"/>
     </row>
     <row r="118">
       <c r="A118" t="s">
@@ -4941,7 +4593,7 @@
         <v>79</v>
       </c>
       <c r="G119" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
         <v>0.660714285714286</v>
@@ -4952,15 +4604,9 @@
       <c r="J119" t="n">
         <v>0.974409546778466</v>
       </c>
-      <c r="K119" t="n">
-        <v>0.0597014925373134</v>
-      </c>
-      <c r="L119" t="n">
-        <v>0.319107142857143</v>
-      </c>
-      <c r="M119" t="n">
-        <v>0.20099924398478</v>
-      </c>
+      <c r="K119"/>
+      <c r="L119"/>
+      <c r="M119"/>
     </row>
     <row r="120">
       <c r="A120" t="s">
@@ -5017,7 +4663,7 @@
         <v>79</v>
       </c>
       <c r="G121" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5028,15 +4674,9 @@
       <c r="J121" t="n">
         <v>0</v>
       </c>
-      <c r="K121" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0.0158928571428571</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0.090856428083261</v>
-      </c>
+      <c r="K121"/>
+      <c r="L121"/>
+      <c r="M121"/>
     </row>
     <row r="122">
       <c r="A122" t="s">
@@ -5093,7 +4733,7 @@
         <v>79</v>
       </c>
       <c r="G123" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
         <v>0.642857142857143</v>
@@ -5104,15 +4744,9 @@
       <c r="J123" t="n">
         <v>0.945960464484689</v>
       </c>
-      <c r="K123" t="n">
-        <v>0.203980099502488</v>
-      </c>
-      <c r="L123" t="n">
-        <v>0.420982142857143</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0.23962845173312</v>
-      </c>
+      <c r="K123"/>
+      <c r="L123"/>
+      <c r="M123"/>
     </row>
     <row r="124">
       <c r="A124" t="s">
@@ -5169,7 +4803,7 @@
         <v>79</v>
       </c>
       <c r="G125" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5180,15 +4814,9 @@
       <c r="J125" t="n">
         <v>0</v>
       </c>
-      <c r="K125" t="n">
-        <v>1</v>
-      </c>
-      <c r="L125" t="n">
-        <v>0.314553571428571</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0.247569701372643</v>
-      </c>
+      <c r="K125"/>
+      <c r="L125"/>
+      <c r="M125"/>
     </row>
     <row r="126">
       <c r="A126" t="s">
@@ -5245,7 +4873,7 @@
         <v>79</v>
       </c>
       <c r="G127" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5256,15 +4884,9 @@
       <c r="J127" t="n">
         <v>0</v>
       </c>
-      <c r="K127" t="n">
-        <v>1</v>
-      </c>
-      <c r="L127" t="n">
-        <v>0.0920535714285714</v>
-      </c>
-      <c r="M127" t="n">
-        <v>0.201435545610708</v>
-      </c>
+      <c r="K127"/>
+      <c r="L127"/>
+      <c r="M127"/>
     </row>
     <row r="128">
       <c r="A128" t="s">
@@ -5321,7 +4943,7 @@
         <v>79</v>
       </c>
       <c r="G129" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>0.375</v>
@@ -5332,15 +4954,9 @@
       <c r="J129" t="n">
         <v>0.692759797890566</v>
       </c>
-      <c r="K129" t="n">
-        <v>0.144278606965174</v>
-      </c>
-      <c r="L129" t="n">
-        <v>0.100446428571429</v>
-      </c>
-      <c r="M129" t="n">
-        <v>0.219723694408278</v>
-      </c>
+      <c r="K129"/>
+      <c r="L129"/>
+      <c r="M129"/>
     </row>
     <row r="130">
       <c r="A130" t="s">
@@ -5397,7 +5013,7 @@
         <v>79</v>
       </c>
       <c r="G131" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -5408,15 +5024,9 @@
       <c r="J131" t="n">
         <v>0</v>
       </c>
-      <c r="K131" t="n">
-        <v>1</v>
-      </c>
-      <c r="L131" t="n">
-        <v>0.2375</v>
-      </c>
-      <c r="M131" t="n">
-        <v>0.239919578106015</v>
-      </c>
+      <c r="K131"/>
+      <c r="L131"/>
+      <c r="M131"/>
     </row>
     <row r="132">
       <c r="A132" t="s">
@@ -5473,7 +5083,7 @@
         <v>79</v>
       </c>
       <c r="G133" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
         <v>0.267857142857143</v>
@@ -5484,15 +5094,9 @@
       <c r="J133" t="n">
         <v>0.54344235441157</v>
       </c>
-      <c r="K133" t="n">
-        <v>0.621890547263682</v>
-      </c>
-      <c r="L133" t="n">
-        <v>0.353303571428571</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0.211105540824327</v>
-      </c>
+      <c r="K133"/>
+      <c r="L133"/>
+      <c r="M133"/>
     </row>
     <row r="134">
       <c r="A134" t="s">
@@ -5549,7 +5153,7 @@
         <v>79</v>
       </c>
       <c r="G135" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -5560,15 +5164,9 @@
       <c r="J135" t="n">
         <v>0</v>
       </c>
-      <c r="K135" t="n">
-        <v>1</v>
-      </c>
-      <c r="L135" t="n">
-        <v>0.0236607142857143</v>
-      </c>
-      <c r="M135" t="n">
-        <v>0.100201978811743</v>
-      </c>
+      <c r="K135"/>
+      <c r="L135"/>
+      <c r="M135"/>
     </row>
     <row r="136">
       <c r="A136" t="s">
@@ -5625,7 +5223,7 @@
         <v>79</v>
       </c>
       <c r="G137" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
         <v>0.678571428571428</v>
@@ -5636,15 +5234,9 @@
       <c r="J137" t="n">
         <v>0.98568953865911</v>
       </c>
-      <c r="K137" t="n">
-        <v>0.18407960199005</v>
-      </c>
-      <c r="L137" t="n">
-        <v>0.449196428571429</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0.219019979681869</v>
-      </c>
+      <c r="K137"/>
+      <c r="L137"/>
+      <c r="M137"/>
     </row>
     <row r="138">
       <c r="A138" t="s">
@@ -5669,13 +5261,13 @@
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>0.339285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0401535615353792</v>
+        <v>0.168318490808307</v>
       </c>
       <c r="J138" t="n">
-        <v>0.638417867036049</v>
+        <v>0.831681509191693</v>
       </c>
       <c r="K138"/>
       <c r="L138"/>
@@ -5701,26 +5293,20 @@
         <v>79</v>
       </c>
       <c r="G139" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>0.339285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="I139" t="n">
-        <v>0.0401535615353792</v>
+        <v>0.168318490808307</v>
       </c>
       <c r="J139" t="n">
-        <v>0.638417867036049</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0.427860696517413</v>
-      </c>
-      <c r="L139" t="n">
-        <v>0.336517857142857</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0.260127755678692</v>
-      </c>
+        <v>0.831681509191693</v>
+      </c>
+      <c r="K139"/>
+      <c r="L139"/>
+      <c r="M139"/>
     </row>
     <row r="140">
       <c r="A140" t="s">
@@ -5777,7 +5363,7 @@
         <v>79</v>
       </c>
       <c r="G141" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -5788,15 +5374,9 @@
       <c r="J141" t="n">
         <v>0</v>
       </c>
-      <c r="K141" t="n">
-        <v>1</v>
-      </c>
-      <c r="L141" t="n">
-        <v>0.105178571428571</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0.22170100821231</v>
-      </c>
+      <c r="K141"/>
+      <c r="L141"/>
+      <c r="M141"/>
     </row>
     <row r="142">
       <c r="A142" t="s">
@@ -5853,7 +5433,7 @@
         <v>79</v>
       </c>
       <c r="G143" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -5864,15 +5444,9 @@
       <c r="J143" t="n">
         <v>0</v>
       </c>
-      <c r="K143" t="n">
-        <v>1</v>
-      </c>
-      <c r="L143" t="n">
-        <v>0.107678571428571</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0.229486779311536</v>
-      </c>
+      <c r="K143"/>
+      <c r="L143"/>
+      <c r="M143"/>
     </row>
     <row r="144">
       <c r="A144" t="s">
@@ -5929,7 +5503,7 @@
         <v>79</v>
       </c>
       <c r="G145" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
         <v>0.125</v>
@@ -5940,15 +5514,9 @@
       <c r="J145" t="n">
         <v>0.369995498067507</v>
       </c>
-      <c r="K145" t="n">
-        <v>0.572139303482587</v>
-      </c>
-      <c r="L145" t="n">
-        <v>0.216696428571429</v>
-      </c>
-      <c r="M145" t="n">
-        <v>0.223664674832714</v>
-      </c>
+      <c r="K145"/>
+      <c r="L145"/>
+      <c r="M145"/>
     </row>
     <row r="146">
       <c r="A146" t="s">
@@ -6005,7 +5573,7 @@
         <v>79</v>
       </c>
       <c r="G147" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
         <v>0.178571428571429</v>
@@ -6016,15 +5584,9 @@
       <c r="J147" t="n">
         <v>0.402155483160153</v>
       </c>
-      <c r="K147" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="L147" t="n">
-        <v>0.308839285714286</v>
-      </c>
-      <c r="M147" t="n">
-        <v>0.21639750792289</v>
-      </c>
+      <c r="K147"/>
+      <c r="L147"/>
+      <c r="M147"/>
     </row>
     <row r="148">
       <c r="A148" t="s">
@@ -6081,7 +5643,7 @@
         <v>79</v>
       </c>
       <c r="G149" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6092,15 +5654,9 @@
       <c r="J149" t="n">
         <v>0</v>
       </c>
-      <c r="K149" t="n">
-        <v>1</v>
-      </c>
-      <c r="L149" t="n">
-        <v>0.0158035714285714</v>
-      </c>
-      <c r="M149" t="n">
-        <v>0.0788535344606292</v>
-      </c>
+      <c r="K149"/>
+      <c r="L149"/>
+      <c r="M149"/>
     </row>
     <row r="150">
       <c r="A150" t="s">
@@ -6157,7 +5713,7 @@
         <v>79</v>
       </c>
       <c r="G151" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
         <v>0.214285714285714</v>
@@ -6168,15 +5724,9 @@
       <c r="J151" t="n">
         <v>0.477751301402942</v>
       </c>
-      <c r="K151" t="n">
-        <v>0.786069651741294</v>
-      </c>
-      <c r="L151" t="n">
-        <v>0.416785714285714</v>
-      </c>
-      <c r="M151" t="n">
-        <v>0.221293349629159</v>
-      </c>
+      <c r="K151"/>
+      <c r="L151"/>
+      <c r="M151"/>
     </row>
     <row r="152">
       <c r="A152" t="s">
@@ -6201,13 +5751,13 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.178571428571429</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>0.219918266894608</v>
+        <v>0.414593220033038</v>
       </c>
       <c r="K152"/>
       <c r="L152"/>
@@ -6233,26 +5783,20 @@
         <v>79</v>
       </c>
       <c r="G153" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.178571428571429</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0.219918266894608</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0.875621890547264</v>
-      </c>
-      <c r="L153" t="n">
-        <v>0.345625</v>
-      </c>
-      <c r="M153" t="n">
-        <v>0.263218981203754</v>
-      </c>
+        <v>0.414593220033038</v>
+      </c>
+      <c r="K153"/>
+      <c r="L153"/>
+      <c r="M153"/>
     </row>
     <row r="154">
       <c r="A154" t="s">
@@ -6309,7 +5853,7 @@
         <v>79</v>
       </c>
       <c r="G155" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H155" t="n">
         <v>0.107142857142857</v>
@@ -6320,15 +5864,9 @@
       <c r="J155" t="n">
         <v>0.320035633676683</v>
       </c>
-      <c r="K155" t="n">
-        <v>0.194029850746269</v>
-      </c>
-      <c r="L155" t="n">
-        <v>0.0734821428571429</v>
-      </c>
-      <c r="M155" t="n">
-        <v>0.187134745766301</v>
-      </c>
+      <c r="K155"/>
+      <c r="L155"/>
+      <c r="M155"/>
     </row>
     <row r="156">
       <c r="A156" t="s">
@@ -6385,7 +5923,7 @@
         <v>79</v>
       </c>
       <c r="G157" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
         <v>0.125</v>
@@ -6396,15 +5934,9 @@
       <c r="J157" t="n">
         <v>0.369995498067507</v>
       </c>
-      <c r="K157" t="n">
-        <v>0.169154228855721</v>
-      </c>
-      <c r="L157" t="n">
-        <v>0.0705357142857143</v>
-      </c>
-      <c r="M157" t="n">
-        <v>0.181964796908967</v>
-      </c>
+      <c r="K157"/>
+      <c r="L157"/>
+      <c r="M157"/>
     </row>
     <row r="158">
       <c r="A158" t="s">
@@ -6461,7 +5993,7 @@
         <v>79</v>
       </c>
       <c r="G159" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
         <v>0.25</v>
@@ -6472,15 +6004,9 @@
       <c r="J159" t="n">
         <v>0.572678126609999</v>
       </c>
-      <c r="K159" t="n">
-        <v>0.343283582089552</v>
-      </c>
-      <c r="L159" t="n">
-        <v>0.206875</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0.242525410416037</v>
-      </c>
+      <c r="K159"/>
+      <c r="L159"/>
+      <c r="M159"/>
     </row>
     <row r="160">
       <c r="A160" t="s">
@@ -6537,7 +6063,7 @@
         <v>79</v>
       </c>
       <c r="G161" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
         <v>0.482142857142857</v>
@@ -6548,15 +6074,9 @@
       <c r="J161" t="n">
         <v>0.816800718226758</v>
       </c>
-      <c r="K161" t="n">
-        <v>0.263681592039801</v>
-      </c>
-      <c r="L161" t="n">
-        <v>0.311160714285714</v>
-      </c>
-      <c r="M161" t="n">
-        <v>0.218179488468298</v>
-      </c>
+      <c r="K161"/>
+      <c r="L161"/>
+      <c r="M161"/>
     </row>
     <row r="162">
       <c r="A162" t="s">
@@ -6613,7 +6133,7 @@
         <v>79</v>
       </c>
       <c r="G163" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -6624,15 +6144,9 @@
       <c r="J163" t="n">
         <v>0</v>
       </c>
-      <c r="K163" t="n">
-        <v>1</v>
-      </c>
-      <c r="L163" t="n">
-        <v>0.0153571428571429</v>
-      </c>
-      <c r="M163" t="n">
-        <v>0.0957217320393703</v>
-      </c>
+      <c r="K163"/>
+      <c r="L163"/>
+      <c r="M163"/>
     </row>
     <row r="164">
       <c r="A164" t="s">
@@ -6689,7 +6203,7 @@
         <v>79</v>
       </c>
       <c r="G165" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H165" t="n">
         <v>0.678571428571429</v>
@@ -6700,15 +6214,9 @@
       <c r="J165" t="n">
         <v>0.977118003952216</v>
       </c>
-      <c r="K165" t="n">
-        <v>0.134328358208955</v>
-      </c>
-      <c r="L165" t="n">
-        <v>0.403660714285714</v>
-      </c>
-      <c r="M165" t="n">
-        <v>0.213505830614023</v>
-      </c>
+      <c r="K165"/>
+      <c r="L165"/>
+      <c r="M165"/>
     </row>
     <row r="166">
       <c r="A166" t="s">
@@ -6733,13 +6241,13 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>0.357142857142857</v>
+        <v>0.232142857142857</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0548103017257365</v>
+        <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>0.659475412559978</v>
+        <v>0.521461465326051</v>
       </c>
       <c r="K166"/>
       <c r="L166"/>
@@ -6765,26 +6273,20 @@
         <v>79</v>
       </c>
       <c r="G167" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>0.357142857142857</v>
+        <v>0.232142857142857</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0548103017257365</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>0.659475412559978</v>
-      </c>
-      <c r="K167" t="n">
-        <v>0.412935323383085</v>
-      </c>
-      <c r="L167" t="n">
-        <v>0.326428571428571</v>
-      </c>
-      <c r="M167" t="n">
-        <v>0.246950688601508</v>
-      </c>
+        <v>0.521461465326051</v>
+      </c>
+      <c r="K167"/>
+      <c r="L167"/>
+      <c r="M167"/>
     </row>
     <row r="168">
       <c r="A168" t="s">
@@ -6841,7 +6343,7 @@
         <v>79</v>
       </c>
       <c r="G169" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -6852,15 +6354,9 @@
       <c r="J169" t="n">
         <v>0</v>
       </c>
-      <c r="K169" t="n">
-        <v>1</v>
-      </c>
-      <c r="L169" t="n">
-        <v>0.0682291666666667</v>
-      </c>
-      <c r="M169" t="n">
-        <v>0.183994277183159</v>
-      </c>
+      <c r="K169"/>
+      <c r="L169"/>
+      <c r="M169"/>
     </row>
     <row r="170">
       <c r="A170" t="s">
@@ -6917,7 +6413,7 @@
         <v>79</v>
       </c>
       <c r="G171" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -6928,15 +6424,9 @@
       <c r="J171" t="n">
         <v>0</v>
       </c>
-      <c r="K171" t="n">
-        <v>1</v>
-      </c>
-      <c r="L171" t="n">
-        <v>0.0696875</v>
-      </c>
-      <c r="M171" t="n">
-        <v>0.183182392514333</v>
-      </c>
+      <c r="K171"/>
+      <c r="L171"/>
+      <c r="M171"/>
     </row>
     <row r="172">
       <c r="A172" t="s">
@@ -6993,7 +6483,7 @@
         <v>79</v>
       </c>
       <c r="G173" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7004,15 +6494,9 @@
       <c r="J173" t="n">
         <v>0</v>
       </c>
-      <c r="K173" t="n">
-        <v>1</v>
-      </c>
-      <c r="L173" t="n">
-        <v>0.157708333333333</v>
-      </c>
-      <c r="M173" t="n">
-        <v>0.230712862909005</v>
-      </c>
+      <c r="K173"/>
+      <c r="L173"/>
+      <c r="M173"/>
     </row>
     <row r="174">
       <c r="A174" t="s">
@@ -7069,7 +6553,7 @@
         <v>79</v>
       </c>
       <c r="G175" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
         <v>0.416666666666667</v>
@@ -7080,15 +6564,9 @@
       <c r="J175" t="n">
         <v>0.76995026657195</v>
       </c>
-      <c r="K175" t="n">
-        <v>0.27363184079602</v>
-      </c>
-      <c r="L175" t="n">
-        <v>0.293333333333333</v>
-      </c>
-      <c r="M175" t="n">
-        <v>0.210513715864978</v>
-      </c>
+      <c r="K175"/>
+      <c r="L175"/>
+      <c r="M175"/>
     </row>
     <row r="176">
       <c r="A176" t="s">
@@ -7145,7 +6623,7 @@
         <v>79</v>
       </c>
       <c r="G177" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -7156,15 +6634,9 @@
       <c r="J177" t="n">
         <v>0</v>
       </c>
-      <c r="K177" t="n">
-        <v>1</v>
-      </c>
-      <c r="L177" t="n">
-        <v>0.0233333333333333</v>
-      </c>
-      <c r="M177" t="n">
-        <v>0.111274656299454</v>
-      </c>
+      <c r="K177"/>
+      <c r="L177"/>
+      <c r="M177"/>
     </row>
     <row r="178">
       <c r="A178" t="s">
@@ -7221,7 +6693,7 @@
         <v>79</v>
       </c>
       <c r="G179" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
         <v>0.291666666666667</v>
@@ -7232,15 +6704,9 @@
       <c r="J179" t="n">
         <v>0.588370949257218</v>
       </c>
-      <c r="K179" t="n">
-        <v>0.716417910447761</v>
-      </c>
-      <c r="L179" t="n">
-        <v>0.419375</v>
-      </c>
-      <c r="M179" t="n">
-        <v>0.225006106840632</v>
-      </c>
+      <c r="K179"/>
+      <c r="L179"/>
+      <c r="M179"/>
     </row>
     <row r="180">
       <c r="A180" t="s">
@@ -7297,7 +6763,7 @@
         <v>79</v>
       </c>
       <c r="G181" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -7308,15 +6774,9 @@
       <c r="J181" t="n">
         <v>0</v>
       </c>
-      <c r="K181" t="n">
-        <v>1</v>
-      </c>
-      <c r="L181" t="n">
-        <v>0.300208333333333</v>
-      </c>
-      <c r="M181" t="n">
-        <v>0.242724519323551</v>
-      </c>
+      <c r="K181"/>
+      <c r="L181"/>
+      <c r="M181"/>
     </row>
     <row r="182">
       <c r="A182" t="s">
@@ -7373,7 +6833,7 @@
         <v>79</v>
       </c>
       <c r="G183" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -7384,15 +6844,9 @@
       <c r="J183" t="n">
         <v>0</v>
       </c>
-      <c r="K183" t="n">
-        <v>1</v>
-      </c>
-      <c r="L183" t="n">
-        <v>0.1115625</v>
-      </c>
-      <c r="M183" t="n">
-        <v>0.230688164317543</v>
-      </c>
+      <c r="K183"/>
+      <c r="L183"/>
+      <c r="M183"/>
     </row>
     <row r="184">
       <c r="A184" t="s">
@@ -7449,7 +6903,7 @@
         <v>79</v>
       </c>
       <c r="G185" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -7460,15 +6914,9 @@
       <c r="J185" t="n">
         <v>0</v>
       </c>
-      <c r="K185" t="n">
-        <v>1</v>
-      </c>
-      <c r="L185" t="n">
-        <v>0.107708333333333</v>
-      </c>
-      <c r="M185" t="n">
-        <v>0.236442387153339</v>
-      </c>
+      <c r="K185"/>
+      <c r="L185"/>
+      <c r="M185"/>
     </row>
     <row r="186">
       <c r="A186" t="s">
@@ -7525,7 +6973,7 @@
         <v>79</v>
       </c>
       <c r="G187" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
         <v>0.104166666666667</v>
@@ -7536,15 +6984,9 @@
       <c r="J187" t="n">
         <v>0.312372804231433</v>
       </c>
-      <c r="K187" t="n">
-        <v>0.442786069651741</v>
-      </c>
-      <c r="L187" t="n">
-        <v>0.177395833333333</v>
-      </c>
-      <c r="M187" t="n">
-        <v>0.25204164851161</v>
-      </c>
+      <c r="K187"/>
+      <c r="L187"/>
+      <c r="M187"/>
     </row>
     <row r="188">
       <c r="A188" t="s">
@@ -7601,7 +7043,7 @@
         <v>79</v>
       </c>
       <c r="G189" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H189" t="n">
         <v>0.25</v>
@@ -7612,15 +7054,9 @@
       <c r="J189" t="n">
         <v>0.53790383878476</v>
       </c>
-      <c r="K189" t="n">
-        <v>0.492537313432836</v>
-      </c>
-      <c r="L189" t="n">
-        <v>0.297083333333333</v>
-      </c>
-      <c r="M189" t="n">
-        <v>0.229240318604571</v>
-      </c>
+      <c r="K189"/>
+      <c r="L189"/>
+      <c r="M189"/>
     </row>
     <row r="190">
       <c r="A190" t="s">
@@ -7677,7 +7113,7 @@
         <v>79</v>
       </c>
       <c r="G191" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -7688,15 +7124,9 @@
       <c r="J191" t="n">
         <v>0</v>
       </c>
-      <c r="K191" t="n">
-        <v>1</v>
-      </c>
-      <c r="L191" t="n">
-        <v>0.0257291666666667</v>
-      </c>
-      <c r="M191" t="n">
-        <v>0.125017054601498</v>
-      </c>
+      <c r="K191"/>
+      <c r="L191"/>
+      <c r="M191"/>
     </row>
     <row r="192">
       <c r="A192" t="s">
@@ -7753,7 +7183,7 @@
         <v>79</v>
       </c>
       <c r="G193" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
         <v>0.25</v>
@@ -7764,15 +7194,9 @@
       <c r="J193" t="n">
         <v>0.530529057727533</v>
       </c>
-      <c r="K193" t="n">
-        <v>0.716417910447761</v>
-      </c>
-      <c r="L193" t="n">
-        <v>0.4228125</v>
-      </c>
-      <c r="M193" t="n">
-        <v>0.257823542455937</v>
-      </c>
+      <c r="K193"/>
+      <c r="L193"/>
+      <c r="M193"/>
     </row>
     <row r="194">
       <c r="A194" t="s">
@@ -7797,13 +7221,13 @@
         <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>0.3125</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>0.641050993082832</v>
+        <v>0.254635630756703</v>
       </c>
       <c r="K194"/>
       <c r="L194"/>
@@ -7829,26 +7253,20 @@
         <v>79</v>
       </c>
       <c r="G195" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>0.3125</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>0.641050993082832</v>
-      </c>
-      <c r="K195" t="n">
-        <v>0.442786069651741</v>
-      </c>
-      <c r="L195" t="n">
-        <v>0.3275</v>
-      </c>
-      <c r="M195" t="n">
-        <v>0.271112309610078</v>
-      </c>
+        <v>0.254635630756703</v>
+      </c>
+      <c r="K195"/>
+      <c r="L195"/>
+      <c r="M195"/>
     </row>
     <row r="196">
       <c r="A196" t="s">
@@ -7905,7 +7323,7 @@
         <v>237</v>
       </c>
       <c r="G197" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -7916,15 +7334,9 @@
       <c r="J197" t="n">
         <v>0</v>
       </c>
-      <c r="K197" t="n">
-        <v>1</v>
-      </c>
-      <c r="L197" t="n">
-        <v>0.0934375</v>
-      </c>
-      <c r="M197" t="n">
-        <v>0.215607690033392</v>
-      </c>
+      <c r="K197"/>
+      <c r="L197"/>
+      <c r="M197"/>
     </row>
     <row r="198">
       <c r="A198" t="s">
@@ -7981,7 +7393,7 @@
         <v>237</v>
       </c>
       <c r="G199" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H199" t="n">
         <v>0.125</v>
@@ -7992,15 +7404,9 @@
       <c r="J199" t="n">
         <v>0.369995498067507</v>
       </c>
-      <c r="K199" t="n">
-        <v>0.233830845771144</v>
-      </c>
-      <c r="L199" t="n">
-        <v>0.0927083333333333</v>
-      </c>
-      <c r="M199" t="n">
-        <v>0.211726451118641</v>
-      </c>
+      <c r="K199"/>
+      <c r="L199"/>
+      <c r="M199"/>
     </row>
     <row r="200">
       <c r="A200" t="s">
@@ -8057,7 +7463,7 @@
         <v>237</v>
       </c>
       <c r="G201" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H201" t="n">
         <v>0.4375</v>
@@ -8068,15 +7474,9 @@
       <c r="J201" t="n">
         <v>0.786032211267904</v>
       </c>
-      <c r="K201" t="n">
-        <v>0.199004975124378</v>
-      </c>
-      <c r="L201" t="n">
-        <v>0.197395833333333</v>
-      </c>
-      <c r="M201" t="n">
-        <v>0.263224498552189</v>
-      </c>
+      <c r="K201"/>
+      <c r="L201"/>
+      <c r="M201"/>
     </row>
     <row r="202">
       <c r="A202" t="s">
@@ -8133,7 +7533,7 @@
         <v>237</v>
       </c>
       <c r="G203" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H203" t="n">
         <v>0.333333333333333</v>
@@ -8144,15 +7544,9 @@
       <c r="J203" t="n">
         <v>0.643230849485614</v>
       </c>
-      <c r="K203" t="n">
-        <v>0.393034825870647</v>
-      </c>
-      <c r="L203" t="n">
-        <v>0.298020833333333</v>
-      </c>
-      <c r="M203" t="n">
-        <v>0.213485266993297</v>
-      </c>
+      <c r="K203"/>
+      <c r="L203"/>
+      <c r="M203"/>
     </row>
     <row r="204">
       <c r="A204" t="s">
@@ -8209,7 +7603,7 @@
         <v>237</v>
       </c>
       <c r="G205" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -8220,15 +7614,9 @@
       <c r="J205" t="n">
         <v>0</v>
       </c>
-      <c r="K205" t="n">
-        <v>1</v>
-      </c>
-      <c r="L205" t="n">
-        <v>0.0167708333333333</v>
-      </c>
-      <c r="M205" t="n">
-        <v>0.0926930108448954</v>
-      </c>
+      <c r="K205"/>
+      <c r="L205"/>
+      <c r="M205"/>
     </row>
     <row r="206">
       <c r="A206" t="s">
@@ -8285,7 +7673,7 @@
         <v>237</v>
       </c>
       <c r="G207" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H207" t="n">
         <v>0.729166666666667</v>
@@ -8296,15 +7684,9 @@
       <c r="J207" t="n">
         <v>1</v>
       </c>
-      <c r="K207" t="n">
-        <v>0.134328358208955</v>
-      </c>
-      <c r="L207" t="n">
-        <v>0.441979166666667</v>
-      </c>
-      <c r="M207" t="n">
-        <v>0.241947700012745</v>
-      </c>
+      <c r="K207"/>
+      <c r="L207"/>
+      <c r="M207"/>
     </row>
     <row r="208">
       <c r="A208" t="s">
@@ -8329,13 +7711,13 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>0.145833333333333</v>
+        <v>0</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
       </c>
       <c r="J208" t="n">
-        <v>0.359460060010976</v>
+        <v>0</v>
       </c>
       <c r="K208"/>
       <c r="L208"/>
@@ -8361,26 +7743,20 @@
         <v>237</v>
       </c>
       <c r="G209" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>0.145833333333333</v>
+        <v>0</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
       </c>
       <c r="J209" t="n">
-        <v>0.359460060010976</v>
-      </c>
-      <c r="K209" t="n">
-        <v>0.686567164179104</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0.330416666666667</v>
-      </c>
-      <c r="M209" t="n">
-        <v>0.258036991643433</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K209"/>
+      <c r="L209"/>
+      <c r="M209"/>
     </row>
     <row r="210">
       <c r="A210" t="s">
@@ -8399,7 +7775,7 @@
         <v>15</v>
       </c>
       <c r="F210" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -8434,10 +7810,10 @@
         <v>15</v>
       </c>
       <c r="F211" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G211" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -8448,15 +7824,9 @@
       <c r="J211" t="n">
         <v>0</v>
       </c>
-      <c r="K211" t="n">
-        <v>1</v>
-      </c>
-      <c r="L211" t="n">
-        <v>0.0990178571428572</v>
-      </c>
-      <c r="M211" t="n">
-        <v>0.208369802896195</v>
-      </c>
+      <c r="K211"/>
+      <c r="L211"/>
+      <c r="M211"/>
     </row>
     <row r="212">
       <c r="A212" t="s">
@@ -8475,7 +7845,7 @@
         <v>15</v>
       </c>
       <c r="F212" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -8510,10 +7880,10 @@
         <v>15</v>
       </c>
       <c r="F213" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G213" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -8524,15 +7894,9 @@
       <c r="J213" t="n">
         <v>0</v>
       </c>
-      <c r="K213" t="n">
-        <v>1</v>
-      </c>
-      <c r="L213" t="n">
-        <v>0.111875</v>
-      </c>
-      <c r="M213" t="n">
-        <v>0.221821588521361</v>
-      </c>
+      <c r="K213"/>
+      <c r="L213"/>
+      <c r="M213"/>
     </row>
     <row r="214">
       <c r="A214" t="s">
@@ -8551,19 +7915,19 @@
         <v>15</v>
       </c>
       <c r="F214" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="I214" t="n">
         <v>0</v>
       </c>
       <c r="J214" t="n">
-        <v>0.498005719950453</v>
+        <v>0.584065413234268</v>
       </c>
       <c r="K214"/>
       <c r="L214"/>
@@ -8586,29 +7950,23 @@
         <v>15</v>
       </c>
       <c r="F215" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G215" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
       <c r="I215" t="n">
         <v>0</v>
       </c>
       <c r="J215" t="n">
-        <v>0.498005719950453</v>
-      </c>
-      <c r="K215" t="n">
-        <v>0.462686567164179</v>
-      </c>
-      <c r="L215" t="n">
-        <v>0.245357142857143</v>
-      </c>
-      <c r="M215" t="n">
-        <v>0.2395803170871</v>
-      </c>
+        <v>0.584065413234268</v>
+      </c>
+      <c r="K215"/>
+      <c r="L215"/>
+      <c r="M215"/>
     </row>
     <row r="216">
       <c r="A216" t="s">
@@ -8627,19 +7985,19 @@
         <v>15</v>
       </c>
       <c r="F216" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>0.392857142857143</v>
+        <v>0.428571428571428</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0632927713151577</v>
+        <v>0.0963627431384117</v>
       </c>
       <c r="J216" t="n">
-        <v>0.722421514399128</v>
+        <v>0.760780114004445</v>
       </c>
       <c r="K216"/>
       <c r="L216"/>
@@ -8662,29 +8020,23 @@
         <v>15</v>
       </c>
       <c r="F217" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G217" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>0.392857142857143</v>
+        <v>0.428571428571428</v>
       </c>
       <c r="I217" t="n">
-        <v>0.0632927713151577</v>
+        <v>0.0963627431384117</v>
       </c>
       <c r="J217" t="n">
-        <v>0.722421514399128</v>
-      </c>
-      <c r="K217" t="n">
-        <v>0.313432835820896</v>
-      </c>
-      <c r="L217" t="n">
-        <v>0.284017857142857</v>
-      </c>
-      <c r="M217" t="n">
-        <v>0.197170314440653</v>
-      </c>
+        <v>0.760780114004445</v>
+      </c>
+      <c r="K217"/>
+      <c r="L217"/>
+      <c r="M217"/>
     </row>
     <row r="218">
       <c r="A218" t="s">
@@ -8703,7 +8055,7 @@
         <v>15</v>
       </c>
       <c r="F218" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -8738,10 +8090,10 @@
         <v>15</v>
       </c>
       <c r="F219" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G219" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -8752,15 +8104,9 @@
       <c r="J219" t="n">
         <v>0</v>
       </c>
-      <c r="K219" t="n">
-        <v>1</v>
-      </c>
-      <c r="L219" t="n">
-        <v>0.00196428571428572</v>
-      </c>
-      <c r="M219" t="n">
-        <v>0.0253671380561481</v>
-      </c>
+      <c r="K219"/>
+      <c r="L219"/>
+      <c r="M219"/>
     </row>
     <row r="220">
       <c r="A220" t="s">
@@ -8779,19 +8125,19 @@
         <v>15</v>
       </c>
       <c r="F220" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>0.392857142857143</v>
+        <v>0.410714285714286</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0462128719888035</v>
+        <v>0.06415416201817</v>
       </c>
       <c r="J220" t="n">
-        <v>0.739501413725482</v>
+        <v>0.757274409410401</v>
       </c>
       <c r="K220"/>
       <c r="L220"/>
@@ -8814,29 +8160,23 @@
         <v>15</v>
       </c>
       <c r="F221" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G221" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H221" t="n">
-        <v>0.392857142857143</v>
+        <v>0.410714285714286</v>
       </c>
       <c r="I221" t="n">
-        <v>0.0462128719888035</v>
+        <v>0.06415416201817</v>
       </c>
       <c r="J221" t="n">
-        <v>0.739501413725482</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0.562189054726368</v>
-      </c>
-      <c r="L221" t="n">
-        <v>0.424285714285714</v>
-      </c>
-      <c r="M221" t="n">
-        <v>0.232423900781298</v>
-      </c>
+        <v>0.757274409410401</v>
+      </c>
+      <c r="K221"/>
+      <c r="L221"/>
+      <c r="M221"/>
     </row>
     <row r="222">
       <c r="A222" t="s">
@@ -8855,19 +8195,19 @@
         <v>15</v>
       </c>
       <c r="F222" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
       </c>
       <c r="H222" t="n">
-        <v>0.142857142857143</v>
+        <v>0.178571428571429</v>
       </c>
       <c r="I222" t="n">
         <v>0</v>
       </c>
       <c r="J222" t="n">
-        <v>0.364080713151928</v>
+        <v>0.436103101473066</v>
       </c>
       <c r="K222"/>
       <c r="L222"/>
@@ -8890,29 +8230,23 @@
         <v>15</v>
       </c>
       <c r="F223" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G223" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>0.142857142857143</v>
+        <v>0.178571428571429</v>
       </c>
       <c r="I223" t="n">
         <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>0.364080713151928</v>
-      </c>
-      <c r="K223" t="n">
-        <v>0.751243781094527</v>
-      </c>
-      <c r="L223" t="n">
-        <v>0.327767857142857</v>
-      </c>
-      <c r="M223" t="n">
-        <v>0.230635933318218</v>
-      </c>
+        <v>0.436103101473066</v>
+      </c>
+      <c r="K223"/>
+      <c r="L223"/>
+      <c r="M223"/>
     </row>
     <row r="224">
       <c r="A224" t="s">
@@ -8931,7 +8265,7 @@
         <v>15</v>
       </c>
       <c r="F224" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -8966,10 +8300,10 @@
         <v>15</v>
       </c>
       <c r="F225" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G225" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -8980,15 +8314,9 @@
       <c r="J225" t="n">
         <v>0</v>
       </c>
-      <c r="K225" t="n">
-        <v>1</v>
-      </c>
-      <c r="L225" t="n">
-        <v>0.101339285714286</v>
-      </c>
-      <c r="M225" t="n">
-        <v>0.234952061537881</v>
-      </c>
+      <c r="K225"/>
+      <c r="L225"/>
+      <c r="M225"/>
     </row>
     <row r="226">
       <c r="A226" t="s">
@@ -9007,7 +8335,7 @@
         <v>15</v>
       </c>
       <c r="F226" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -9042,10 +8370,10 @@
         <v>15</v>
       </c>
       <c r="F227" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G227" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -9056,15 +8384,9 @@
       <c r="J227" t="n">
         <v>0</v>
       </c>
-      <c r="K227" t="n">
-        <v>1</v>
-      </c>
-      <c r="L227" t="n">
-        <v>0.102410714285714</v>
-      </c>
-      <c r="M227" t="n">
-        <v>0.227541350833974</v>
-      </c>
+      <c r="K227"/>
+      <c r="L227"/>
+      <c r="M227"/>
     </row>
     <row r="228">
       <c r="A228" t="s">
@@ -9083,7 +8405,7 @@
         <v>15</v>
       </c>
       <c r="F228" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -9118,10 +8440,10 @@
         <v>15</v>
       </c>
       <c r="F229" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G229" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -9132,15 +8454,9 @@
       <c r="J229" t="n">
         <v>0</v>
       </c>
-      <c r="K229" t="n">
-        <v>1</v>
-      </c>
-      <c r="L229" t="n">
-        <v>0.306160714285714</v>
-      </c>
-      <c r="M229" t="n">
-        <v>0.254562998007102</v>
-      </c>
+      <c r="K229"/>
+      <c r="L229"/>
+      <c r="M229"/>
     </row>
     <row r="230">
       <c r="A230" t="s">
@@ -9159,19 +8475,19 @@
         <v>15</v>
       </c>
       <c r="F230" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>0.0535714285714286</v>
+        <v>0</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>0.157171326650143</v>
+        <v>0</v>
       </c>
       <c r="K230"/>
       <c r="L230"/>
@@ -9194,29 +8510,23 @@
         <v>15</v>
       </c>
       <c r="F231" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G231" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>0.0535714285714286</v>
+        <v>0</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
       </c>
       <c r="J231" t="n">
-        <v>0.157171326650143</v>
-      </c>
-      <c r="K231" t="n">
-        <v>0.915422885572139</v>
-      </c>
-      <c r="L231" t="n">
-        <v>0.340803571428571</v>
-      </c>
-      <c r="M231" t="n">
-        <v>0.222839976899532</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K231"/>
+      <c r="L231"/>
+      <c r="M231"/>
     </row>
     <row r="232">
       <c r="A232" t="s">
@@ -9235,7 +8545,7 @@
         <v>15</v>
       </c>
       <c r="F232" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -9270,10 +8580,10 @@
         <v>15</v>
       </c>
       <c r="F233" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G233" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -9284,15 +8594,9 @@
       <c r="J233" t="n">
         <v>0</v>
       </c>
-      <c r="K233" t="n">
-        <v>1</v>
-      </c>
-      <c r="L233" t="n">
-        <v>0.0351785714285714</v>
-      </c>
-      <c r="M233" t="n">
-        <v>0.140583463224855</v>
-      </c>
+      <c r="K233"/>
+      <c r="L233"/>
+      <c r="M233"/>
     </row>
     <row r="234">
       <c r="A234" t="s">
@@ -9311,7 +8615,7 @@
         <v>15</v>
       </c>
       <c r="F234" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -9346,10 +8650,10 @@
         <v>15</v>
       </c>
       <c r="F235" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G235" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -9360,15 +8664,9 @@
       <c r="J235" t="n">
         <v>0</v>
       </c>
-      <c r="K235" t="n">
-        <v>1</v>
-      </c>
-      <c r="L235" t="n">
-        <v>0.453392857142857</v>
-      </c>
-      <c r="M235" t="n">
-        <v>0.24831365149962</v>
-      </c>
+      <c r="K235"/>
+      <c r="L235"/>
+      <c r="M235"/>
     </row>
     <row r="236">
       <c r="A236" t="s">
@@ -9387,19 +8685,19 @@
         <v>15</v>
       </c>
       <c r="F236" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
       </c>
       <c r="H236" t="n">
-        <v>0.392857142857143</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="I236" t="n">
-        <v>0.064001512719451</v>
+        <v>0.0588895015827412</v>
       </c>
       <c r="J236" t="n">
-        <v>0.721712772994835</v>
+        <v>0.655396212702973</v>
       </c>
       <c r="K236"/>
       <c r="L236"/>
@@ -9422,29 +8720,23 @@
         <v>15</v>
       </c>
       <c r="F237" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G237" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H237" t="n">
-        <v>0.392857142857143</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="I237" t="n">
-        <v>0.064001512719451</v>
+        <v>0.0588895015827412</v>
       </c>
       <c r="J237" t="n">
-        <v>0.721712772994835</v>
-      </c>
-      <c r="K237" t="n">
-        <v>0.378109452736318</v>
-      </c>
-      <c r="L237" t="n">
-        <v>0.327142857142857</v>
-      </c>
-      <c r="M237" t="n">
-        <v>0.261636672378901</v>
-      </c>
+        <v>0.655396212702973</v>
+      </c>
+      <c r="K237"/>
+      <c r="L237"/>
+      <c r="M237"/>
     </row>
     <row r="238">
       <c r="A238" t="s">
@@ -9463,7 +8755,7 @@
         <v>15</v>
       </c>
       <c r="F238" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -9498,10 +8790,10 @@
         <v>15</v>
       </c>
       <c r="F239" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G239" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -9512,15 +8804,9 @@
       <c r="J239" t="n">
         <v>0</v>
       </c>
-      <c r="K239" t="n">
-        <v>1</v>
-      </c>
-      <c r="L239" t="n">
-        <v>0.0909821428571428</v>
-      </c>
-      <c r="M239" t="n">
-        <v>0.202185886225931</v>
-      </c>
+      <c r="K239"/>
+      <c r="L239"/>
+      <c r="M239"/>
     </row>
     <row r="240">
       <c r="A240" t="s">
@@ -9539,7 +8825,7 @@
         <v>15</v>
       </c>
       <c r="F240" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -9574,10 +8860,10 @@
         <v>15</v>
       </c>
       <c r="F241" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G241" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -9588,15 +8874,9 @@
       <c r="J241" t="n">
         <v>0</v>
       </c>
-      <c r="K241" t="n">
-        <v>1</v>
-      </c>
-      <c r="L241" t="n">
-        <v>0.0804464285714286</v>
-      </c>
-      <c r="M241" t="n">
-        <v>0.192992673091462</v>
-      </c>
+      <c r="K241"/>
+      <c r="L241"/>
+      <c r="M241"/>
     </row>
     <row r="242">
       <c r="A242" t="s">
@@ -9615,19 +8895,19 @@
         <v>15</v>
       </c>
       <c r="F242" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.107142857142857</v>
       </c>
       <c r="I242" t="n">
         <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>0.270021615983094</v>
+        <v>0.320035633676683</v>
       </c>
       <c r="K242"/>
       <c r="L242"/>
@@ -9650,29 +8930,23 @@
         <v>15</v>
       </c>
       <c r="F243" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G243" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H243" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.107142857142857</v>
       </c>
       <c r="I243" t="n">
         <v>0</v>
       </c>
       <c r="J243" t="n">
-        <v>0.270021615983094</v>
-      </c>
-      <c r="K243" t="n">
-        <v>0.706467661691542</v>
-      </c>
-      <c r="L243" t="n">
-        <v>0.250892857142857</v>
-      </c>
-      <c r="M243" t="n">
-        <v>0.240431637520497</v>
-      </c>
+        <v>0.320035633676683</v>
+      </c>
+      <c r="K243"/>
+      <c r="L243"/>
+      <c r="M243"/>
     </row>
     <row r="244">
       <c r="A244" t="s">
@@ -9691,19 +8965,19 @@
         <v>15</v>
       </c>
       <c r="F244" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
       </c>
       <c r="H244" t="n">
-        <v>0.214285714285714</v>
+        <v>0.303571428571429</v>
       </c>
       <c r="I244" t="n">
-        <v>0</v>
+        <v>0.0105466667246532</v>
       </c>
       <c r="J244" t="n">
-        <v>0.468397160033926</v>
+        <v>0.596596190418204</v>
       </c>
       <c r="K244"/>
       <c r="L244"/>
@@ -9726,29 +9000,23 @@
         <v>15</v>
       </c>
       <c r="F245" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G245" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>0.214285714285714</v>
+        <v>0.303571428571429</v>
       </c>
       <c r="I245" t="n">
-        <v>0</v>
+        <v>0.0105466667246532</v>
       </c>
       <c r="J245" t="n">
-        <v>0.468397160033926</v>
-      </c>
-      <c r="K245" t="n">
-        <v>0.592039800995025</v>
-      </c>
-      <c r="L245" t="n">
-        <v>0.288839285714286</v>
-      </c>
-      <c r="M245" t="n">
-        <v>0.212403777674221</v>
-      </c>
+        <v>0.596596190418204</v>
+      </c>
+      <c r="K245"/>
+      <c r="L245"/>
+      <c r="M245"/>
     </row>
     <row r="246">
       <c r="A246" t="s">
@@ -9767,7 +9035,7 @@
         <v>15</v>
       </c>
       <c r="F246" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -9802,10 +9070,10 @@
         <v>15</v>
       </c>
       <c r="F247" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G247" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -9816,15 +9084,9 @@
       <c r="J247" t="n">
         <v>0</v>
       </c>
-      <c r="K247" t="n">
-        <v>1</v>
-      </c>
-      <c r="L247" t="n">
-        <v>0.0257142857142857</v>
-      </c>
-      <c r="M247" t="n">
-        <v>0.129373544827054</v>
-      </c>
+      <c r="K247"/>
+      <c r="L247"/>
+      <c r="M247"/>
     </row>
     <row r="248">
       <c r="A248" t="s">
@@ -9843,19 +9105,19 @@
         <v>15</v>
       </c>
       <c r="F248" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
       </c>
       <c r="H248" t="n">
-        <v>0.464285714285714</v>
+        <v>0.535714285714286</v>
       </c>
       <c r="I248" t="n">
-        <v>0.133749304679759</v>
+        <v>0.179935307443837</v>
       </c>
       <c r="J248" t="n">
-        <v>0.794822123891669</v>
+        <v>0.891493263984734</v>
       </c>
       <c r="K248"/>
       <c r="L248"/>
@@ -9878,29 +9140,23 @@
         <v>15</v>
       </c>
       <c r="F249" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G249" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H249" t="n">
-        <v>0.464285714285714</v>
+        <v>0.535714285714286</v>
       </c>
       <c r="I249" t="n">
-        <v>0.133749304679759</v>
+        <v>0.179935307443837</v>
       </c>
       <c r="J249" t="n">
-        <v>0.794822123891669</v>
-      </c>
-      <c r="K249" t="n">
-        <v>0.432835820895522</v>
-      </c>
-      <c r="L249" t="n">
-        <v>0.428035714285714</v>
-      </c>
-      <c r="M249" t="n">
-        <v>0.226789635715146</v>
-      </c>
+        <v>0.891493263984734</v>
+      </c>
+      <c r="K249"/>
+      <c r="L249"/>
+      <c r="M249"/>
     </row>
     <row r="250">
       <c r="A250" t="s">
@@ -9919,19 +9175,19 @@
         <v>15</v>
       </c>
       <c r="F250" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
       </c>
       <c r="H250" t="n">
-        <v>0.285714285714286</v>
+        <v>0.196428571428571</v>
       </c>
       <c r="I250" t="n">
         <v>0</v>
       </c>
       <c r="J250" t="n">
-        <v>0.595762347183268</v>
+        <v>0.454864660363769</v>
       </c>
       <c r="K250"/>
       <c r="L250"/>
@@ -9954,29 +9210,23 @@
         <v>15</v>
       </c>
       <c r="F251" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G251" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H251" t="n">
-        <v>0.285714285714286</v>
+        <v>0.196428571428571</v>
       </c>
       <c r="I251" t="n">
         <v>0</v>
       </c>
       <c r="J251" t="n">
-        <v>0.595762347183268</v>
-      </c>
-      <c r="K251" t="n">
-        <v>0.532338308457711</v>
-      </c>
-      <c r="L251" t="n">
-        <v>0.354642857142857</v>
-      </c>
-      <c r="M251" t="n">
-        <v>0.265070089975714</v>
-      </c>
+        <v>0.454864660363769</v>
+      </c>
+      <c r="K251"/>
+      <c r="L251"/>
+      <c r="M251"/>
     </row>
     <row r="252">
       <c r="A252" t="s">
@@ -9995,7 +9245,7 @@
         <v>15</v>
       </c>
       <c r="F252" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10030,10 +9280,10 @@
         <v>15</v>
       </c>
       <c r="F253" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G253" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -10044,15 +9294,9 @@
       <c r="J253" t="n">
         <v>0</v>
       </c>
-      <c r="K253" t="n">
-        <v>1</v>
-      </c>
-      <c r="L253" t="n">
-        <v>0.0946428571428572</v>
-      </c>
-      <c r="M253" t="n">
-        <v>0.209361034739988</v>
-      </c>
+      <c r="K253"/>
+      <c r="L253"/>
+      <c r="M253"/>
     </row>
     <row r="254">
       <c r="A254" t="s">
@@ -10071,19 +9315,19 @@
         <v>15</v>
       </c>
       <c r="F254" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
       </c>
       <c r="H254" t="n">
-        <v>0.232142857142857</v>
+        <v>0</v>
       </c>
       <c r="I254" t="n">
         <v>0</v>
       </c>
       <c r="J254" t="n">
-        <v>0.533218709048258</v>
+        <v>0</v>
       </c>
       <c r="K254"/>
       <c r="L254"/>
@@ -10106,29 +9350,23 @@
         <v>15</v>
       </c>
       <c r="F255" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G255" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H255" t="n">
-        <v>0.232142857142857</v>
+        <v>0</v>
       </c>
       <c r="I255" t="n">
         <v>0</v>
       </c>
       <c r="J255" t="n">
-        <v>0.533218709048258</v>
-      </c>
-      <c r="K255" t="n">
-        <v>0.144278606965174</v>
-      </c>
-      <c r="L255" t="n">
-        <v>0.0985714285714286</v>
-      </c>
-      <c r="M255" t="n">
-        <v>0.211007467567123</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K255"/>
+      <c r="L255"/>
+      <c r="M255"/>
     </row>
     <row r="256">
       <c r="A256" t="s">
@@ -10147,19 +9385,19 @@
         <v>15</v>
       </c>
       <c r="F256" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>0.232142857142857</v>
+        <v>0.482142857142857</v>
       </c>
       <c r="I256" t="n">
-        <v>0</v>
+        <v>0.153198550819075</v>
       </c>
       <c r="J256" t="n">
-        <v>0.539925007162735</v>
+        <v>0.811087163466639</v>
       </c>
       <c r="K256"/>
       <c r="L256"/>
@@ -10182,29 +9420,23 @@
         <v>15</v>
       </c>
       <c r="F257" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G257" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H257" t="n">
-        <v>0.232142857142857</v>
+        <v>0.482142857142857</v>
       </c>
       <c r="I257" t="n">
-        <v>0</v>
+        <v>0.153198550819075</v>
       </c>
       <c r="J257" t="n">
-        <v>0.539925007162735</v>
-      </c>
-      <c r="K257" t="n">
-        <v>0.447761194029851</v>
-      </c>
-      <c r="L257" t="n">
-        <v>0.239375</v>
-      </c>
-      <c r="M257" t="n">
-        <v>0.238130289879202</v>
-      </c>
+        <v>0.811087163466639</v>
+      </c>
+      <c r="K257"/>
+      <c r="L257"/>
+      <c r="M257"/>
     </row>
     <row r="258">
       <c r="A258" t="s">
@@ -10223,19 +9455,19 @@
         <v>15</v>
       </c>
       <c r="F258" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>0.517857142857143</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="I258" t="n">
-        <v>0.18311214263335</v>
+        <v>0.048981898179589</v>
       </c>
       <c r="J258" t="n">
-        <v>0.852602143080936</v>
+        <v>0.665303816106125</v>
       </c>
       <c r="K258"/>
       <c r="L258"/>
@@ -10258,29 +9490,23 @@
         <v>15</v>
       </c>
       <c r="F259" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G259" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>0.517857142857143</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="I259" t="n">
-        <v>0.18311214263335</v>
+        <v>0.048981898179589</v>
       </c>
       <c r="J259" t="n">
-        <v>0.852602143080936</v>
-      </c>
-      <c r="K259" t="n">
-        <v>0.169154228855721</v>
-      </c>
-      <c r="L259" t="n">
-        <v>0.284285714285714</v>
-      </c>
-      <c r="M259" t="n">
-        <v>0.213163789487333</v>
-      </c>
+        <v>0.665303816106125</v>
+      </c>
+      <c r="K259"/>
+      <c r="L259"/>
+      <c r="M259"/>
     </row>
     <row r="260">
       <c r="A260" t="s">
@@ -10299,7 +9525,7 @@
         <v>15</v>
       </c>
       <c r="F260" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -10334,10 +9560,10 @@
         <v>15</v>
       </c>
       <c r="F261" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G261" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -10348,15 +9574,9 @@
       <c r="J261" t="n">
         <v>0</v>
       </c>
-      <c r="K261" t="n">
-        <v>1</v>
-      </c>
-      <c r="L261" t="n">
-        <v>0.01375</v>
-      </c>
-      <c r="M261" t="n">
-        <v>0.100931304575227</v>
-      </c>
+      <c r="K261"/>
+      <c r="L261"/>
+      <c r="M261"/>
     </row>
     <row r="262">
       <c r="A262" t="s">
@@ -10375,19 +9595,19 @@
         <v>15</v>
       </c>
       <c r="F262" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G262" t="n">
         <v>0</v>
       </c>
       <c r="H262" t="n">
-        <v>0.482142857142857</v>
+        <v>0.464285714285714</v>
       </c>
       <c r="I262" t="n">
-        <v>0.161095801432675</v>
+        <v>0.147537160902876</v>
       </c>
       <c r="J262" t="n">
-        <v>0.803189912853039</v>
+        <v>0.781034267668553</v>
       </c>
       <c r="K262"/>
       <c r="L262"/>
@@ -10410,29 +9630,23 @@
         <v>15</v>
       </c>
       <c r="F263" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G263" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H263" t="n">
-        <v>0.482142857142857</v>
+        <v>0.464285714285714</v>
       </c>
       <c r="I263" t="n">
-        <v>0.161095801432675</v>
+        <v>0.147537160902876</v>
       </c>
       <c r="J263" t="n">
-        <v>0.803189912853039</v>
-      </c>
-      <c r="K263" t="n">
-        <v>0.36318407960199</v>
-      </c>
-      <c r="L263" t="n">
-        <v>0.398839285714286</v>
-      </c>
-      <c r="M263" t="n">
-        <v>0.237147024214376</v>
-      </c>
+        <v>0.781034267668553</v>
+      </c>
+      <c r="K263"/>
+      <c r="L263"/>
+      <c r="M263"/>
     </row>
     <row r="264">
       <c r="A264" t="s">
@@ -10451,19 +9665,19 @@
         <v>15</v>
       </c>
       <c r="F264" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
       </c>
       <c r="H264" t="n">
-        <v>0</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="I264" t="n">
         <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>0</v>
+        <v>0.422851997791436</v>
       </c>
       <c r="K264"/>
       <c r="L264"/>
@@ -10486,29 +9700,23 @@
         <v>15</v>
       </c>
       <c r="F265" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G265" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H265" t="n">
-        <v>0</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="I265" t="n">
         <v>0</v>
       </c>
       <c r="J265" t="n">
-        <v>0</v>
-      </c>
-      <c r="K265" t="n">
-        <v>1</v>
-      </c>
-      <c r="L265" t="n">
-        <v>0.329553571428571</v>
-      </c>
-      <c r="M265" t="n">
-        <v>0.250184512338043</v>
-      </c>
+        <v>0.422851997791436</v>
+      </c>
+      <c r="K265"/>
+      <c r="L265"/>
+      <c r="M265"/>
     </row>
     <row r="266">
       <c r="A266" t="s">
@@ -10527,7 +9735,7 @@
         <v>14</v>
       </c>
       <c r="F266" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G266" t="n">
         <v>0</v>
@@ -10562,10 +9770,10 @@
         <v>14</v>
       </c>
       <c r="F267" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G267" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -10576,15 +9784,9 @@
       <c r="J267" t="n">
         <v>0</v>
       </c>
-      <c r="K267" t="n">
-        <v>1</v>
-      </c>
-      <c r="L267" t="n">
-        <v>0.0908333333333334</v>
-      </c>
-      <c r="M267" t="n">
-        <v>0.204391519774347</v>
-      </c>
+      <c r="K267"/>
+      <c r="L267"/>
+      <c r="M267"/>
     </row>
     <row r="268">
       <c r="A268" t="s">
@@ -10603,7 +9805,7 @@
         <v>14</v>
       </c>
       <c r="F268" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -10638,10 +9840,10 @@
         <v>14</v>
       </c>
       <c r="F269" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G269" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -10652,15 +9854,9 @@
       <c r="J269" t="n">
         <v>0</v>
       </c>
-      <c r="K269" t="n">
-        <v>1</v>
-      </c>
-      <c r="L269" t="n">
-        <v>0.112291666666667</v>
-      </c>
-      <c r="M269" t="n">
-        <v>0.231348020106149</v>
-      </c>
+      <c r="K269"/>
+      <c r="L269"/>
+      <c r="M269"/>
     </row>
     <row r="270">
       <c r="A270" t="s">
@@ -10679,7 +9875,7 @@
         <v>14</v>
       </c>
       <c r="F270" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -10714,10 +9910,10 @@
         <v>14</v>
       </c>
       <c r="F271" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G271" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -10728,15 +9924,9 @@
       <c r="J271" t="n">
         <v>0</v>
       </c>
-      <c r="K271" t="n">
-        <v>1</v>
-      </c>
-      <c r="L271" t="n">
-        <v>0.174739583333333</v>
-      </c>
-      <c r="M271" t="n">
-        <v>0.254629879127735</v>
-      </c>
+      <c r="K271"/>
+      <c r="L271"/>
+      <c r="M271"/>
     </row>
     <row r="272">
       <c r="A272" t="s">
@@ -10755,19 +9945,19 @@
         <v>14</v>
       </c>
       <c r="F272" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>0</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="I272" t="n">
         <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>0</v>
+        <v>0.138294194204506</v>
       </c>
       <c r="K272"/>
       <c r="L272"/>
@@ -10790,29 +9980,23 @@
         <v>14</v>
       </c>
       <c r="F273" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G273" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>0</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="I273" t="n">
         <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>0</v>
-      </c>
-      <c r="K273" t="n">
-        <v>1</v>
-      </c>
-      <c r="L273" t="n">
-        <v>0.271041666666667</v>
-      </c>
-      <c r="M273" t="n">
-        <v>0.198050129116888</v>
-      </c>
+        <v>0.138294194204506</v>
+      </c>
+      <c r="K273"/>
+      <c r="L273"/>
+      <c r="M273"/>
     </row>
     <row r="274">
       <c r="A274" t="s">
@@ -10831,7 +10015,7 @@
         <v>14</v>
       </c>
       <c r="F274" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
@@ -10866,10 +10050,10 @@
         <v>14</v>
       </c>
       <c r="F275" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G275" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -10880,15 +10064,9 @@
       <c r="J275" t="n">
         <v>0</v>
       </c>
-      <c r="K275" t="n">
-        <v>1</v>
-      </c>
-      <c r="L275" t="n">
-        <v>0.0204166666666667</v>
-      </c>
-      <c r="M275" t="n">
-        <v>0.0923928144435703</v>
-      </c>
+      <c r="K275"/>
+      <c r="L275"/>
+      <c r="M275"/>
     </row>
     <row r="276">
       <c r="A276" t="s">
@@ -10907,7 +10085,7 @@
         <v>14</v>
       </c>
       <c r="F276" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
@@ -10919,7 +10097,7 @@
         <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>0.526672637512813</v>
+        <v>0.49630040275005</v>
       </c>
       <c r="K276"/>
       <c r="L276"/>
@@ -10942,10 +10120,10 @@
         <v>14</v>
       </c>
       <c r="F277" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G277" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H277" t="n">
         <v>0.229166666666667</v>
@@ -10954,17 +10132,11 @@
         <v>0</v>
       </c>
       <c r="J277" t="n">
-        <v>0.526672637512813</v>
-      </c>
-      <c r="K277" t="n">
-        <v>0.736318407960199</v>
-      </c>
-      <c r="L277" t="n">
-        <v>0.421770833333333</v>
-      </c>
-      <c r="M277" t="n">
-        <v>0.259759409277899</v>
-      </c>
+        <v>0.49630040275005</v>
+      </c>
+      <c r="K277"/>
+      <c r="L277"/>
+      <c r="M277"/>
     </row>
     <row r="278">
       <c r="A278" t="s">
@@ -10983,19 +10155,19 @@
         <v>14</v>
       </c>
       <c r="F278" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
       </c>
       <c r="H278" t="n">
-        <v>0.25</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I278" t="n">
-        <v>0</v>
+        <v>0.0302749192283137</v>
       </c>
       <c r="J278" t="n">
-        <v>0.52085271413872</v>
+        <v>0.636391747438353</v>
       </c>
       <c r="K278"/>
       <c r="L278"/>
@@ -11018,29 +10190,23 @@
         <v>14</v>
       </c>
       <c r="F279" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G279" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>0.25</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="I279" t="n">
-        <v>0</v>
+        <v>0.0302749192283137</v>
       </c>
       <c r="J279" t="n">
-        <v>0.52085271413872</v>
-      </c>
-      <c r="K279" t="n">
-        <v>0.562189054726368</v>
-      </c>
-      <c r="L279" t="n">
-        <v>0.332916666666667</v>
-      </c>
-      <c r="M279" t="n">
-        <v>0.263539359749836</v>
-      </c>
+        <v>0.636391747438353</v>
+      </c>
+      <c r="K279"/>
+      <c r="L279"/>
+      <c r="M279"/>
     </row>
     <row r="280">
       <c r="A280" t="s">
@@ -11059,7 +10225,7 @@
         <v>14</v>
       </c>
       <c r="F280" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -11094,10 +10260,10 @@
         <v>14</v>
       </c>
       <c r="F281" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G281" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -11108,15 +10274,9 @@
       <c r="J281" t="n">
         <v>0</v>
       </c>
-      <c r="K281" t="n">
-        <v>1</v>
-      </c>
-      <c r="L281" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="M281" t="n">
-        <v>0.160167460174393</v>
-      </c>
+      <c r="K281"/>
+      <c r="L281"/>
+      <c r="M281"/>
     </row>
     <row r="282">
       <c r="A282" t="s">
@@ -11135,7 +10295,7 @@
         <v>14</v>
       </c>
       <c r="F282" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G282" t="n">
         <v>0</v>
@@ -11170,10 +10330,10 @@
         <v>14</v>
       </c>
       <c r="F283" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G283" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -11184,15 +10344,9 @@
       <c r="J283" t="n">
         <v>0</v>
       </c>
-      <c r="K283" t="n">
-        <v>1</v>
-      </c>
-      <c r="L283" t="n">
-        <v>0.0710416666666667</v>
-      </c>
-      <c r="M283" t="n">
-        <v>0.189256268487786</v>
-      </c>
+      <c r="K283"/>
+      <c r="L283"/>
+      <c r="M283"/>
     </row>
     <row r="284">
       <c r="A284" t="s">
@@ -11211,7 +10365,7 @@
         <v>14</v>
       </c>
       <c r="F284" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G284" t="n">
         <v>0</v>
@@ -11246,10 +10400,10 @@
         <v>14</v>
       </c>
       <c r="F285" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G285" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -11260,15 +10414,9 @@
       <c r="J285" t="n">
         <v>0</v>
       </c>
-      <c r="K285" t="n">
-        <v>1</v>
-      </c>
-      <c r="L285" t="n">
-        <v>0.185833333333333</v>
-      </c>
-      <c r="M285" t="n">
-        <v>0.251568571628405</v>
-      </c>
+      <c r="K285"/>
+      <c r="L285"/>
+      <c r="M285"/>
     </row>
     <row r="286">
       <c r="A286" t="s">
@@ -11287,19 +10435,19 @@
         <v>14</v>
       </c>
       <c r="F286" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G286" t="n">
         <v>0</v>
       </c>
       <c r="H286" t="n">
-        <v>0.270833333333333</v>
+        <v>0.1875</v>
       </c>
       <c r="I286" t="n">
         <v>0</v>
       </c>
       <c r="J286" t="n">
-        <v>0.618818397935346</v>
+        <v>0.456411092588118</v>
       </c>
       <c r="K286"/>
       <c r="L286"/>
@@ -11322,29 +10470,23 @@
         <v>14</v>
       </c>
       <c r="F287" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G287" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>0.270833333333333</v>
+        <v>0.1875</v>
       </c>
       <c r="I287" t="n">
         <v>0</v>
       </c>
       <c r="J287" t="n">
-        <v>0.618818397935346</v>
-      </c>
-      <c r="K287" t="n">
-        <v>0.447761194029851</v>
-      </c>
-      <c r="L287" t="n">
-        <v>0.264583333333333</v>
-      </c>
-      <c r="M287" t="n">
-        <v>0.212910358532692</v>
-      </c>
+        <v>0.456411092588118</v>
+      </c>
+      <c r="K287"/>
+      <c r="L287"/>
+      <c r="M287"/>
     </row>
     <row r="288">
       <c r="A288" t="s">
@@ -11363,7 +10505,7 @@
         <v>14</v>
       </c>
       <c r="F288" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G288" t="n">
         <v>0</v>
@@ -11398,10 +10540,10 @@
         <v>14</v>
       </c>
       <c r="F289" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G289" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -11412,15 +10554,9 @@
       <c r="J289" t="n">
         <v>0</v>
       </c>
-      <c r="K289" t="n">
-        <v>1</v>
-      </c>
-      <c r="L289" t="n">
-        <v>0.0157291666666667</v>
-      </c>
-      <c r="M289" t="n">
-        <v>0.115919807854461</v>
-      </c>
+      <c r="K289"/>
+      <c r="L289"/>
+      <c r="M289"/>
     </row>
     <row r="290">
       <c r="A290" t="s">
@@ -11439,19 +10575,19 @@
         <v>14</v>
       </c>
       <c r="F290" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G290" t="n">
         <v>0</v>
       </c>
       <c r="H290" t="n">
-        <v>0.229166666666667</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I290" t="n">
         <v>0</v>
       </c>
       <c r="J290" t="n">
-        <v>0.559741310164942</v>
+        <v>0.424175688469012</v>
       </c>
       <c r="K290"/>
       <c r="L290"/>
@@ -11474,29 +10610,23 @@
         <v>14</v>
       </c>
       <c r="F291" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G291" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H291" t="n">
-        <v>0.229166666666667</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I291" t="n">
         <v>0</v>
       </c>
       <c r="J291" t="n">
-        <v>0.559741310164942</v>
-      </c>
-      <c r="K291" t="n">
-        <v>0.741293532338308</v>
-      </c>
-      <c r="L291" t="n">
-        <v>0.421041666666667</v>
-      </c>
-      <c r="M291" t="n">
-        <v>0.245533363958673</v>
-      </c>
+        <v>0.424175688469012</v>
+      </c>
+      <c r="K291"/>
+      <c r="L291"/>
+      <c r="M291"/>
     </row>
     <row r="292">
       <c r="A292" t="s">
@@ -11515,19 +10645,19 @@
         <v>14</v>
       </c>
       <c r="F292" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G292" t="n">
         <v>0</v>
       </c>
       <c r="H292" t="n">
-        <v>0.479166666666667</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="I292" t="n">
-        <v>0.101256438988135</v>
+        <v>0.166412912013105</v>
       </c>
       <c r="J292" t="n">
-        <v>0.857076894345199</v>
+        <v>0.916920421320228</v>
       </c>
       <c r="K292"/>
       <c r="L292"/>
@@ -11550,29 +10680,23 @@
         <v>14</v>
       </c>
       <c r="F293" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G293" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H293" t="n">
-        <v>0.479166666666667</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="I293" t="n">
-        <v>0.101256438988135</v>
+        <v>0.166412912013105</v>
       </c>
       <c r="J293" t="n">
-        <v>0.857076894345199</v>
-      </c>
-      <c r="K293" t="n">
-        <v>0.283582089552239</v>
-      </c>
-      <c r="L293" t="n">
-        <v>0.320520833333333</v>
-      </c>
-      <c r="M293" t="n">
-        <v>0.263379729993166</v>
-      </c>
+        <v>0.916920421320228</v>
+      </c>
+      <c r="K293"/>
+      <c r="L293"/>
+      <c r="M293"/>
     </row>
     <row r="294">
       <c r="A294" t="s">
@@ -11591,7 +10715,7 @@
         <v>14</v>
       </c>
       <c r="F294" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G294" t="n">
         <v>0</v>
@@ -11626,10 +10750,10 @@
         <v>14</v>
       </c>
       <c r="F295" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G295" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -11640,15 +10764,9 @@
       <c r="J295" t="n">
         <v>0</v>
       </c>
-      <c r="K295" t="n">
-        <v>1</v>
-      </c>
-      <c r="L295" t="n">
-        <v>0.04625</v>
-      </c>
-      <c r="M295" t="n">
-        <v>0.137324452681594</v>
-      </c>
+      <c r="K295"/>
+      <c r="L295"/>
+      <c r="M295"/>
     </row>
     <row r="296">
       <c r="A296" t="s">
@@ -11667,7 +10785,7 @@
         <v>14</v>
       </c>
       <c r="F296" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -11702,10 +10820,10 @@
         <v>14</v>
       </c>
       <c r="F297" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G297" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -11716,15 +10834,9 @@
       <c r="J297" t="n">
         <v>0</v>
       </c>
-      <c r="K297" t="n">
-        <v>1</v>
-      </c>
-      <c r="L297" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-      <c r="M297" t="n">
-        <v>0.16368245428363</v>
-      </c>
+      <c r="K297"/>
+      <c r="L297"/>
+      <c r="M297"/>
     </row>
     <row r="298">
       <c r="A298" t="s">
@@ -11743,7 +10855,7 @@
         <v>14</v>
       </c>
       <c r="F298" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G298" t="n">
         <v>0</v>
@@ -11778,10 +10890,10 @@
         <v>14</v>
       </c>
       <c r="F299" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G299" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H299" t="n">
         <v>0.125</v>
@@ -11792,15 +10904,9 @@
       <c r="J299" t="n">
         <v>0.369995498067507</v>
       </c>
-      <c r="K299" t="n">
-        <v>0.417910447761194</v>
-      </c>
-      <c r="L299" t="n">
-        <v>0.160833333333333</v>
-      </c>
-      <c r="M299" t="n">
-        <v>0.236062035084323</v>
-      </c>
+      <c r="K299"/>
+      <c r="L299"/>
+      <c r="M299"/>
     </row>
     <row r="300">
       <c r="A300" t="s">
@@ -11819,19 +10925,19 @@
         <v>14</v>
       </c>
       <c r="F300" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G300" t="n">
         <v>0</v>
       </c>
       <c r="H300" t="n">
-        <v>0.270833333333333</v>
+        <v>0.229166666666667</v>
       </c>
       <c r="I300" t="n">
         <v>0</v>
       </c>
       <c r="J300" t="n">
-        <v>0.55119252785563</v>
+        <v>0.495228289784367</v>
       </c>
       <c r="K300"/>
       <c r="L300"/>
@@ -11854,29 +10960,23 @@
         <v>14</v>
       </c>
       <c r="F301" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G301" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H301" t="n">
-        <v>0.270833333333333</v>
+        <v>0.229166666666667</v>
       </c>
       <c r="I301" t="n">
         <v>0</v>
       </c>
       <c r="J301" t="n">
-        <v>0.55119252785563</v>
-      </c>
-      <c r="K301" t="n">
-        <v>0.378109452736318</v>
-      </c>
-      <c r="L301" t="n">
-        <v>0.216770833333333</v>
-      </c>
-      <c r="M301" t="n">
-        <v>0.19408002749784</v>
-      </c>
+        <v>0.495228289784367</v>
+      </c>
+      <c r="K301"/>
+      <c r="L301"/>
+      <c r="M301"/>
     </row>
     <row r="302">
       <c r="A302" t="s">
@@ -11895,7 +10995,7 @@
         <v>14</v>
       </c>
       <c r="F302" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G302" t="n">
         <v>0</v>
@@ -11930,10 +11030,10 @@
         <v>14</v>
       </c>
       <c r="F303" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G303" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -11944,15 +11044,9 @@
       <c r="J303" t="n">
         <v>0</v>
       </c>
-      <c r="K303" t="n">
-        <v>1</v>
-      </c>
-      <c r="L303" t="n">
-        <v>0.0078125</v>
-      </c>
-      <c r="M303" t="n">
-        <v>0.0735291487559752</v>
-      </c>
+      <c r="K303"/>
+      <c r="L303"/>
+      <c r="M303"/>
     </row>
     <row r="304">
       <c r="A304" t="s">
@@ -11971,7 +11065,7 @@
         <v>14</v>
       </c>
       <c r="F304" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G304" t="n">
         <v>0</v>
@@ -12006,10 +11100,10 @@
         <v>14</v>
       </c>
       <c r="F305" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G305" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H305" t="n">
         <v>0.270833333333333</v>
@@ -12020,15 +11114,9 @@
       <c r="J305" t="n">
         <v>0.551871364671475</v>
       </c>
-      <c r="K305" t="n">
-        <v>0.641791044776119</v>
-      </c>
-      <c r="L305" t="n">
-        <v>0.4065625</v>
-      </c>
-      <c r="M305" t="n">
-        <v>0.256731483928585</v>
-      </c>
+      <c r="K305"/>
+      <c r="L305"/>
+      <c r="M305"/>
     </row>
     <row r="306">
       <c r="A306" t="s">
@@ -12047,19 +11135,19 @@
         <v>14</v>
       </c>
       <c r="F306" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G306" t="n">
         <v>0</v>
       </c>
       <c r="H306" t="n">
-        <v>0.145833333333333</v>
+        <v>0.229166666666667</v>
       </c>
       <c r="I306" t="n">
         <v>0</v>
       </c>
       <c r="J306" t="n">
-        <v>0.391799114398261</v>
+        <v>0.49630040275005</v>
       </c>
       <c r="K306"/>
       <c r="L306"/>
@@ -12082,29 +11170,23 @@
         <v>14</v>
       </c>
       <c r="F307" t="n">
-        <v>5711</v>
+        <v>5696</v>
       </c>
       <c r="G307" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H307" t="n">
-        <v>0.145833333333333</v>
+        <v>0.229166666666667</v>
       </c>
       <c r="I307" t="n">
         <v>0</v>
       </c>
       <c r="J307" t="n">
-        <v>0.391799114398261</v>
-      </c>
-      <c r="K307" t="n">
-        <v>0.73134328358209</v>
-      </c>
-      <c r="L307" t="n">
-        <v>0.35125</v>
-      </c>
-      <c r="M307" t="n">
-        <v>0.260015729885382</v>
-      </c>
+        <v>0.49630040275005</v>
+      </c>
+      <c r="K307"/>
+      <c r="L307"/>
+      <c r="M307"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/05_Figures/F05_classification/c_data/results.xlsx
+++ b/05_Figures/F05_classification/c_data/results.xlsx
@@ -533,7 +533,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -544,9 +544,15 @@
       <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0694642857142857</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.199209335364792</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -603,7 +609,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -614,9 +620,15 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5"/>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0728571428571428</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.216483110032967</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -673,7 +685,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
         <v>0.196428571428571</v>
@@ -684,9 +696,15 @@
       <c r="J7" t="n">
         <v>0.465263732604026</v>
       </c>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
+      <c r="K7" t="n">
+        <v>0.263681592039801</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.138035714285714</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.181664790036149</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -743,7 +761,7 @@
         <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H9" t="n">
         <v>0.455357142857143</v>
@@ -754,9 +772,15 @@
       <c r="J9" t="n">
         <v>0.742677897497216</v>
       </c>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
+      <c r="K9" t="n">
+        <v>0.606965174129353</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5065625</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.197424296848772</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -813,7 +837,7 @@
         <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H11" t="n">
         <v>0.5</v>
@@ -824,9 +848,15 @@
       <c r="J11" t="n">
         <v>0.823490578067923</v>
       </c>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
+      <c r="K11" t="n">
+        <v>0.298507462686567</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.368303571428571</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.203488112035621</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -883,7 +913,7 @@
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -894,9 +924,15 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0238392857142857</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.112187953893319</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -953,7 +989,7 @@
         <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" t="n">
         <v>0.5</v>
@@ -964,9 +1000,15 @@
       <c r="J15" t="n">
         <v>0.823219987825617</v>
       </c>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
+      <c r="K15" t="n">
+        <v>0.373134328358209</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.410089285714286</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.213726968807571</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -991,13 +1033,13 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.482142857142857</v>
+        <v>0.339285714285714</v>
       </c>
       <c r="I16" t="n">
-        <v>0.153730967094126</v>
+        <v>0.0299911121600566</v>
       </c>
       <c r="J16" t="n">
-        <v>0.810554747191589</v>
+        <v>0.648580316411372</v>
       </c>
       <c r="K16"/>
       <c r="L16"/>
@@ -1023,20 +1065,26 @@
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H17" t="n">
-        <v>0.482142857142857</v>
+        <v>0.339285714285714</v>
       </c>
       <c r="I17" t="n">
-        <v>0.153730967094126</v>
+        <v>0.0299911121600566</v>
       </c>
       <c r="J17" t="n">
-        <v>0.810554747191589</v>
-      </c>
-      <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17"/>
+        <v>0.648580316411372</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.393034825870647</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.305982142857143</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.251078827400813</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -1093,7 +1141,7 @@
         <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1104,9 +1152,15 @@
       <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19"/>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0658928571428571</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.186553391087878</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -1163,7 +1217,7 @@
         <v>12</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1174,9 +1228,15 @@
       <c r="J21" t="n">
         <v>0</v>
       </c>
-      <c r="K21"/>
-      <c r="L21"/>
-      <c r="M21"/>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0757142857142857</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.206053277165054</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -1233,7 +1293,7 @@
         <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1244,9 +1304,15 @@
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="K23"/>
-      <c r="L23"/>
-      <c r="M23"/>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.194464285714286</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.234766839494559</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
@@ -1303,7 +1369,7 @@
         <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H25" t="n">
         <v>0.732142857142857</v>
@@ -1314,9 +1380,15 @@
       <c r="J25" t="n">
         <v>0.990578946078055</v>
       </c>
-      <c r="K25"/>
-      <c r="L25"/>
-      <c r="M25"/>
+      <c r="K25" t="n">
+        <v>0.139303482587065</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.518883928571429</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.180024101817027</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
@@ -1373,7 +1445,7 @@
         <v>12</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H27" t="n">
         <v>0.285714285714286</v>
@@ -1384,9 +1456,15 @@
       <c r="J27" t="n">
         <v>0.560345362108269</v>
       </c>
-      <c r="K27"/>
-      <c r="L27"/>
-      <c r="M27"/>
+      <c r="K27" t="n">
+        <v>0.641791044776119</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.383303571428571</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.219697730525772</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
@@ -1443,7 +1521,7 @@
         <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1454,9 +1532,15 @@
       <c r="J29" t="n">
         <v>0</v>
       </c>
-      <c r="K29"/>
-      <c r="L29"/>
-      <c r="M29"/>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.15793582152458</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
@@ -1513,7 +1597,7 @@
         <v>12</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H31" t="n">
         <v>0.303571428571429</v>
@@ -1524,9 +1608,15 @@
       <c r="J31" t="n">
         <v>0.59066369748579</v>
       </c>
-      <c r="K31"/>
-      <c r="L31"/>
-      <c r="M31"/>
+      <c r="K31" t="n">
+        <v>0.751243781094527</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.223011142306527</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
@@ -1551,13 +1641,13 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.125</v>
+        <v>0.160714285714286</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.372482825776728</v>
+        <v>0.37401765621979</v>
       </c>
       <c r="K32"/>
       <c r="L32"/>
@@ -1583,20 +1673,26 @@
         <v>12</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H33" t="n">
-        <v>0.125</v>
+        <v>0.160714285714286</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.372482825776728</v>
-      </c>
-      <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
+        <v>0.37401765621979</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.601990049751244</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.296428571428571</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.259991598359084</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
@@ -1653,7 +1749,7 @@
         <v>12</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1664,9 +1760,15 @@
       <c r="J35" t="n">
         <v>0</v>
       </c>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.0630357142857143</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.184180656849469</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
@@ -1723,7 +1825,7 @@
         <v>12</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1734,9 +1836,15 @@
       <c r="J37" t="n">
         <v>0</v>
       </c>
-      <c r="K37"/>
-      <c r="L37"/>
-      <c r="M37"/>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.0573214285714286</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.172153047837694</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
@@ -1793,7 +1901,7 @@
         <v>12</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1804,9 +1912,15 @@
       <c r="J39" t="n">
         <v>0</v>
       </c>
-      <c r="K39"/>
-      <c r="L39"/>
-      <c r="M39"/>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.153125</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.205860306981865</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
@@ -1863,7 +1977,7 @@
         <v>12</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H41" t="n">
         <v>0.321428571428571</v>
@@ -1874,9 +1988,15 @@
       <c r="J41" t="n">
         <v>0.553588040690332</v>
       </c>
-      <c r="K41"/>
-      <c r="L41"/>
-      <c r="M41"/>
+      <c r="K41" t="n">
+        <v>0.880597014925373</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.507276785714286</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.184520600647326</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
@@ -1933,7 +2053,7 @@
         <v>12</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H43" t="n">
         <v>0.339285714285714</v>
@@ -1944,9 +2064,15 @@
       <c r="J43" t="n">
         <v>0.638222802031445</v>
       </c>
-      <c r="K43"/>
-      <c r="L43"/>
-      <c r="M43"/>
+      <c r="K43" t="n">
+        <v>0.582089552238806</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.369196428571429</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.22997522904937</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
@@ -2003,7 +2129,7 @@
         <v>12</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2014,9 +2140,15 @@
       <c r="J45" t="n">
         <v>0</v>
       </c>
-      <c r="K45"/>
-      <c r="L45"/>
-      <c r="M45"/>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.0284821428571429</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.131455663300222</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
@@ -2073,7 +2205,7 @@
         <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H47" t="n">
         <v>0.321428571428571</v>
@@ -2084,9 +2216,15 @@
       <c r="J47" t="n">
         <v>0.619486286852477</v>
       </c>
-      <c r="K47"/>
-      <c r="L47"/>
-      <c r="M47"/>
+      <c r="K47" t="n">
+        <v>0.686567164179104</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.422053571428571</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.212228228880443</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
@@ -2111,13 +2249,13 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.271628188926489</v>
+        <v>0.221092116746228</v>
       </c>
       <c r="K48"/>
       <c r="L48"/>
@@ -2143,20 +2281,26 @@
         <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.271628188926489</v>
-      </c>
-      <c r="K49"/>
-      <c r="L49"/>
-      <c r="M49"/>
+        <v>0.221092116746228</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.825870646766169</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.306339285714286</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.237523899854849</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
@@ -2213,7 +2357,7 @@
         <v>12</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2224,9 +2368,15 @@
       <c r="J51" t="n">
         <v>0</v>
       </c>
-      <c r="K51"/>
-      <c r="L51"/>
-      <c r="M51"/>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.0603571428571428</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.181945510533236</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
@@ -2283,7 +2433,7 @@
         <v>12</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2294,9 +2444,15 @@
       <c r="J53" t="n">
         <v>0</v>
       </c>
-      <c r="K53"/>
-      <c r="L53"/>
-      <c r="M53"/>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.0603571428571428</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.189401994651296</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
@@ -2353,7 +2509,7 @@
         <v>12</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H55" t="n">
         <v>0.0892857142857143</v>
@@ -2364,9 +2520,15 @@
       <c r="J55" t="n">
         <v>0.270021615983094</v>
       </c>
-      <c r="K55"/>
-      <c r="L55"/>
-      <c r="M55"/>
+      <c r="K55" t="n">
+        <v>0.412935323383085</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.125535714285714</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.189768394725123</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
@@ -2423,7 +2585,7 @@
         <v>12</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H57" t="n">
         <v>0.383928571428571</v>
@@ -2434,9 +2596,15 @@
       <c r="J57" t="n">
         <v>0.662277996708847</v>
       </c>
-      <c r="K57"/>
-      <c r="L57"/>
-      <c r="M57"/>
+      <c r="K57" t="n">
+        <v>0.761194029850746</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.509732142857143</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.183228902390461</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
@@ -2493,7 +2661,7 @@
         <v>12</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H59" t="n">
         <v>0.321428571428571</v>
@@ -2504,9 +2672,15 @@
       <c r="J59" t="n">
         <v>0.629873331795623</v>
       </c>
-      <c r="K59"/>
-      <c r="L59"/>
-      <c r="M59"/>
+      <c r="K59" t="n">
+        <v>0.512437810945274</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.343035714285714</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.211550729513821</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
@@ -2563,7 +2737,7 @@
         <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2574,9 +2748,15 @@
       <c r="J61" t="n">
         <v>0</v>
       </c>
-      <c r="K61"/>
-      <c r="L61"/>
-      <c r="M61"/>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.0297321428571428</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.137487442439411</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
@@ -2633,7 +2813,7 @@
         <v>12</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H63" t="n">
         <v>0.446428571428571</v>
@@ -2644,9 +2824,15 @@
       <c r="J63" t="n">
         <v>0.776523500391919</v>
       </c>
-      <c r="K63"/>
-      <c r="L63"/>
-      <c r="M63"/>
+      <c r="K63" t="n">
+        <v>0.3681592039801</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.377767857142857</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.226416177411875</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
@@ -2671,13 +2857,13 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.422851997791436</v>
+        <v>0</v>
       </c>
       <c r="K64"/>
       <c r="L64"/>
@@ -2703,20 +2889,26 @@
         <v>12</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H65" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.422851997791436</v>
-      </c>
-      <c r="K65"/>
-      <c r="L65"/>
-      <c r="M65"/>
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.280446428571429</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.247635194608436</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
@@ -2773,7 +2965,7 @@
         <v>12</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2784,9 +2976,15 @@
       <c r="J67" t="n">
         <v>0</v>
       </c>
-      <c r="K67"/>
-      <c r="L67"/>
-      <c r="M67"/>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.0451041666666667</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.155394819138373</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
@@ -2843,7 +3041,7 @@
         <v>12</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2854,9 +3052,15 @@
       <c r="J69" t="n">
         <v>0</v>
       </c>
-      <c r="K69"/>
-      <c r="L69"/>
-      <c r="M69"/>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.0451041666666667</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.159098168969622</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
@@ -2913,7 +3117,7 @@
         <v>12</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2924,9 +3128,15 @@
       <c r="J71" t="n">
         <v>0</v>
       </c>
-      <c r="K71"/>
-      <c r="L71"/>
-      <c r="M71"/>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.104895833333333</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.180384208601723</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
@@ -2983,7 +3193,7 @@
         <v>12</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H73" t="n">
         <v>0.354166666666667</v>
@@ -2994,9 +3204,15 @@
       <c r="J73" t="n">
         <v>0.627731913068815</v>
       </c>
-      <c r="K73"/>
-      <c r="L73"/>
-      <c r="M73"/>
+      <c r="K73" t="n">
+        <v>0.890547263681592</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.562604166666667</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.248828192280237</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
@@ -3053,7 +3269,7 @@
         <v>12</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H75" t="n">
         <v>0.4375</v>
@@ -3064,9 +3280,15 @@
       <c r="J75" t="n">
         <v>0.790918415250738</v>
       </c>
-      <c r="K75"/>
-      <c r="L75"/>
-      <c r="M75"/>
+      <c r="K75" t="n">
+        <v>0.278606965174129</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.319479166666667</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.20154646107937</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
@@ -3123,7 +3345,7 @@
         <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3134,9 +3356,15 @@
       <c r="J77" t="n">
         <v>0</v>
       </c>
-      <c r="K77"/>
-      <c r="L77"/>
-      <c r="M77"/>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.0276041666666667</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.131512003852555</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
@@ -3193,7 +3421,7 @@
         <v>12</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H79" t="n">
         <v>0.270833333333333</v>
@@ -3204,9 +3432,15 @@
       <c r="J79" t="n">
         <v>0.580269348833198</v>
       </c>
-      <c r="K79"/>
-      <c r="L79"/>
-      <c r="M79"/>
+      <c r="K79" t="n">
+        <v>0.701492537313433</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.384479166666667</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.218828976929277</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
@@ -3231,13 +3465,13 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>0.0377204632497903</v>
       </c>
       <c r="J80" t="n">
-        <v>0.537572724427035</v>
+        <v>0.71227953675021</v>
       </c>
       <c r="K80"/>
       <c r="L80"/>
@@ -3263,20 +3497,26 @@
         <v>12</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H81" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>0.0377204632497903</v>
       </c>
       <c r="J81" t="n">
-        <v>0.537572724427035</v>
-      </c>
-      <c r="K81"/>
-      <c r="L81"/>
-      <c r="M81"/>
+        <v>0.71227953675021</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.343283582089552</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.296770833333333</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.25374513246453</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
@@ -3333,7 +3573,7 @@
         <v>12</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -3344,9 +3584,15 @@
       <c r="J83" t="n">
         <v>0</v>
       </c>
-      <c r="K83"/>
-      <c r="L83"/>
-      <c r="M83"/>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.0759374999999999</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.197883851859551</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
@@ -3403,7 +3649,7 @@
         <v>12</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3414,9 +3660,15 @@
       <c r="J85" t="n">
         <v>0</v>
       </c>
-      <c r="K85"/>
-      <c r="L85"/>
-      <c r="M85"/>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.0841666666666667</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.210694740962718</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
@@ -3473,7 +3725,7 @@
         <v>12</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -3484,9 +3736,15 @@
       <c r="J87" t="n">
         <v>0</v>
       </c>
-      <c r="K87"/>
-      <c r="L87"/>
-      <c r="M87"/>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.142395833333333</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.221119144989096</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
@@ -3543,7 +3801,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H89" t="n">
         <v>0.645833333333333</v>
@@ -3554,9 +3812,15 @@
       <c r="J89" t="n">
         <v>0.935140180358442</v>
       </c>
-      <c r="K89"/>
-      <c r="L89"/>
-      <c r="M89"/>
+      <c r="K89" t="n">
+        <v>0.26865671641791</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.511770833333333</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.19818044773011</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
@@ -3613,7 +3877,7 @@
         <v>12</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H91" t="n">
         <v>0.104166666666667</v>
@@ -3624,9 +3888,15 @@
       <c r="J91" t="n">
         <v>0.285991235629427</v>
       </c>
-      <c r="K91"/>
-      <c r="L91"/>
-      <c r="M91"/>
+      <c r="K91" t="n">
+        <v>0.850746268656716</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.343333333333333</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.21735050247666</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
@@ -3683,7 +3953,7 @@
         <v>12</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3694,9 +3964,15 @@
       <c r="J93" t="n">
         <v>0</v>
       </c>
-      <c r="K93"/>
-      <c r="L93"/>
-      <c r="M93"/>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.0298958333333334</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.14050255619149</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
@@ -3753,7 +4029,7 @@
         <v>12</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H95" t="n">
         <v>0.229166666666667</v>
@@ -3764,9 +4040,15 @@
       <c r="J95" t="n">
         <v>0.526992708579932</v>
       </c>
-      <c r="K95"/>
-      <c r="L95"/>
-      <c r="M95"/>
+      <c r="K95" t="n">
+        <v>0.761194029850746</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.417604166666667</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.22714769902877</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
@@ -3791,13 +4073,13 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0.104166666666667</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0.312372804231433</v>
+        <v>0.406553437642822</v>
       </c>
       <c r="K96"/>
       <c r="L96"/>
@@ -3823,20 +4105,26 @@
         <v>12</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H97" t="n">
-        <v>0.104166666666667</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0.312372804231433</v>
-      </c>
-      <c r="K97"/>
-      <c r="L97"/>
-      <c r="M97"/>
+        <v>0.406553437642822</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.611940298507463</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.296770833333333</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.25582529133498</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
@@ -3893,7 +4181,7 @@
         <v>36</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3904,9 +4192,15 @@
       <c r="J99" t="n">
         <v>0</v>
       </c>
-      <c r="K99"/>
-      <c r="L99"/>
-      <c r="M99"/>
+      <c r="K99" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.0741666666666666</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.199636744373565</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
@@ -3963,7 +4257,7 @@
         <v>36</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3974,9 +4268,15 @@
       <c r="J101" t="n">
         <v>0</v>
       </c>
-      <c r="K101"/>
-      <c r="L101"/>
-      <c r="M101"/>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.0742708333333334</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.197505220080637</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
@@ -4033,7 +4333,7 @@
         <v>36</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4044,9 +4344,15 @@
       <c r="J103" t="n">
         <v>0</v>
       </c>
-      <c r="K103"/>
-      <c r="L103"/>
-      <c r="M103"/>
+      <c r="K103" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.183125</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.23398029998035</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
@@ -4103,7 +4409,7 @@
         <v>36</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H105" t="n">
         <v>0.1875</v>
@@ -4114,9 +4420,15 @@
       <c r="J105" t="n">
         <v>0.430739235294357</v>
       </c>
-      <c r="K105"/>
-      <c r="L105"/>
-      <c r="M105"/>
+      <c r="K105" t="n">
+        <v>0.706467661691542</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.335625</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.216635156676656</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
@@ -4173,7 +4485,7 @@
         <v>36</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -4184,9 +4496,15 @@
       <c r="J107" t="n">
         <v>0</v>
       </c>
-      <c r="K107"/>
-      <c r="L107"/>
-      <c r="M107"/>
+      <c r="K107" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.0040625</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.0337867959661506</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
@@ -4243,7 +4561,7 @@
         <v>36</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H109" t="n">
         <v>0.333333333333333</v>
@@ -4254,9 +4572,15 @@
       <c r="J109" t="n">
         <v>0.6561801364455</v>
       </c>
-      <c r="K109"/>
-      <c r="L109"/>
-      <c r="M109"/>
+      <c r="K109" t="n">
+        <v>0.651741293532338</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.425520833333333</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.221441057805316</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
@@ -4281,13 +4605,13 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.104166666666667</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0.31689955374757</v>
+        <v>0.139275209482804</v>
       </c>
       <c r="K110"/>
       <c r="L110"/>
@@ -4313,20 +4637,26 @@
         <v>36</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H111" t="n">
-        <v>0.104166666666667</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0.31689955374757</v>
-      </c>
-      <c r="K111"/>
-      <c r="L111"/>
-      <c r="M111"/>
+        <v>0.139275209482804</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.890547263681592</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.335208333333333</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.257488266985894</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
@@ -4383,7 +4713,7 @@
         <v>79</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H113" t="n">
         <v>0.142857142857143</v>
@@ -4394,9 +4724,15 @@
       <c r="J113" t="n">
         <v>0.422851997791436</v>
       </c>
-      <c r="K113"/>
-      <c r="L113"/>
-      <c r="M113"/>
+      <c r="K113" t="n">
+        <v>0.199004975124378</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.105982142857143</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.225962638790841</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
@@ -4453,7 +4789,7 @@
         <v>79</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H115" t="n">
         <v>0.321428571428571</v>
@@ -4464,9 +4800,15 @@
       <c r="J115" t="n">
         <v>0.647612706214414</v>
       </c>
-      <c r="K115"/>
-      <c r="L115"/>
-      <c r="M115"/>
+      <c r="K115" t="n">
+        <v>0.169154228855721</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.116071428571429</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.252519099882679</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
@@ -4523,7 +4865,7 @@
         <v>79</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H117" t="n">
         <v>0.125</v>
@@ -4534,9 +4876,15 @@
       <c r="J117" t="n">
         <v>0.372482825776728</v>
       </c>
-      <c r="K117"/>
-      <c r="L117"/>
-      <c r="M117"/>
+      <c r="K117" t="n">
+        <v>0.572139303482587</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.213839285714286</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.221206421660859</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
@@ -4593,7 +4941,7 @@
         <v>79</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H119" t="n">
         <v>0.660714285714286</v>
@@ -4604,9 +4952,15 @@
       <c r="J119" t="n">
         <v>0.974409546778466</v>
       </c>
-      <c r="K119"/>
-      <c r="L119"/>
-      <c r="M119"/>
+      <c r="K119" t="n">
+        <v>0.0597014925373134</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.319107142857143</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.20099924398478</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
@@ -4663,7 +5017,7 @@
         <v>79</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -4674,9 +5028,15 @@
       <c r="J121" t="n">
         <v>0</v>
       </c>
-      <c r="K121"/>
-      <c r="L121"/>
-      <c r="M121"/>
+      <c r="K121" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.0158928571428571</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.090856428083261</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
@@ -4733,7 +5093,7 @@
         <v>79</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H123" t="n">
         <v>0.642857142857143</v>
@@ -4744,9 +5104,15 @@
       <c r="J123" t="n">
         <v>0.945960464484689</v>
       </c>
-      <c r="K123"/>
-      <c r="L123"/>
-      <c r="M123"/>
+      <c r="K123" t="n">
+        <v>0.203980099502488</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.420982142857143</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.23962845173312</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
@@ -4803,7 +5169,7 @@
         <v>79</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4814,9 +5180,15 @@
       <c r="J125" t="n">
         <v>0</v>
       </c>
-      <c r="K125"/>
-      <c r="L125"/>
-      <c r="M125"/>
+      <c r="K125" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.314642857142857</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.238489772425645</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
@@ -4873,7 +5245,7 @@
         <v>79</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4884,9 +5256,15 @@
       <c r="J127" t="n">
         <v>0</v>
       </c>
-      <c r="K127"/>
-      <c r="L127"/>
-      <c r="M127"/>
+      <c r="K127" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.0920535714285714</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.201435545610708</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
@@ -4943,7 +5321,7 @@
         <v>79</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H129" t="n">
         <v>0.375</v>
@@ -4954,9 +5332,15 @@
       <c r="J129" t="n">
         <v>0.692759797890566</v>
       </c>
-      <c r="K129"/>
-      <c r="L129"/>
-      <c r="M129"/>
+      <c r="K129" t="n">
+        <v>0.144278606965174</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.100446428571429</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.219723694408278</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
@@ -5013,7 +5397,7 @@
         <v>79</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -5024,9 +5408,15 @@
       <c r="J131" t="n">
         <v>0</v>
       </c>
-      <c r="K131"/>
-      <c r="L131"/>
-      <c r="M131"/>
+      <c r="K131" t="n">
+        <v>1</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.239919578106015</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
@@ -5083,7 +5473,7 @@
         <v>79</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H133" t="n">
         <v>0.267857142857143</v>
@@ -5094,9 +5484,15 @@
       <c r="J133" t="n">
         <v>0.54344235441157</v>
       </c>
-      <c r="K133"/>
-      <c r="L133"/>
-      <c r="M133"/>
+      <c r="K133" t="n">
+        <v>0.621890547263682</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.353303571428571</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.211105540824327</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
@@ -5153,7 +5549,7 @@
         <v>79</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -5164,9 +5560,15 @@
       <c r="J135" t="n">
         <v>0</v>
       </c>
-      <c r="K135"/>
-      <c r="L135"/>
-      <c r="M135"/>
+      <c r="K135" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.0236607142857143</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.100201978811743</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
@@ -5223,7 +5625,7 @@
         <v>79</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H137" t="n">
         <v>0.678571428571428</v>
@@ -5234,9 +5636,15 @@
       <c r="J137" t="n">
         <v>0.98568953865911</v>
       </c>
-      <c r="K137"/>
-      <c r="L137"/>
-      <c r="M137"/>
+      <c r="K137" t="n">
+        <v>0.18407960199005</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.449196428571429</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.219019979681869</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
@@ -5261,13 +5669,13 @@
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>0.5</v>
+        <v>0.446428571428571</v>
       </c>
       <c r="I138" t="n">
-        <v>0.168318490808307</v>
+        <v>0.13069450138736</v>
       </c>
       <c r="J138" t="n">
-        <v>0.831681509191693</v>
+        <v>0.762162641469783</v>
       </c>
       <c r="K138"/>
       <c r="L138"/>
@@ -5293,20 +5701,26 @@
         <v>79</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H139" t="n">
-        <v>0.5</v>
+        <v>0.446428571428571</v>
       </c>
       <c r="I139" t="n">
-        <v>0.168318490808307</v>
+        <v>0.13069450138736</v>
       </c>
       <c r="J139" t="n">
-        <v>0.831681509191693</v>
-      </c>
-      <c r="K139"/>
-      <c r="L139"/>
-      <c r="M139"/>
+        <v>0.762162641469783</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.348258706467662</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.335535714285714</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.254413092607442</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
@@ -5363,7 +5777,7 @@
         <v>79</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -5374,9 +5788,15 @@
       <c r="J141" t="n">
         <v>0</v>
       </c>
-      <c r="K141"/>
-      <c r="L141"/>
-      <c r="M141"/>
+      <c r="K141" t="n">
+        <v>1</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.105178571428571</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.22170100821231</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
@@ -5433,7 +5853,7 @@
         <v>79</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -5444,9 +5864,15 @@
       <c r="J143" t="n">
         <v>0</v>
       </c>
-      <c r="K143"/>
-      <c r="L143"/>
-      <c r="M143"/>
+      <c r="K143" t="n">
+        <v>1</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.107678571428571</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.229486779311536</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
@@ -5503,7 +5929,7 @@
         <v>79</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H145" t="n">
         <v>0.125</v>
@@ -5514,9 +5940,15 @@
       <c r="J145" t="n">
         <v>0.369995498067507</v>
       </c>
-      <c r="K145"/>
-      <c r="L145"/>
-      <c r="M145"/>
+      <c r="K145" t="n">
+        <v>0.572139303482587</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.216696428571429</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.223664674832714</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
@@ -5573,7 +6005,7 @@
         <v>79</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H147" t="n">
         <v>0.178571428571429</v>
@@ -5584,9 +6016,15 @@
       <c r="J147" t="n">
         <v>0.402155483160153</v>
       </c>
-      <c r="K147"/>
-      <c r="L147"/>
-      <c r="M147"/>
+      <c r="K147" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0.308839285714286</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.21639750792289</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
@@ -5643,7 +6081,7 @@
         <v>79</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -5654,9 +6092,15 @@
       <c r="J149" t="n">
         <v>0</v>
       </c>
-      <c r="K149"/>
-      <c r="L149"/>
-      <c r="M149"/>
+      <c r="K149" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0.0158035714285714</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.0788535344606292</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
@@ -5713,7 +6157,7 @@
         <v>79</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H151" t="n">
         <v>0.214285714285714</v>
@@ -5724,9 +6168,15 @@
       <c r="J151" t="n">
         <v>0.477751301402942</v>
       </c>
-      <c r="K151"/>
-      <c r="L151"/>
-      <c r="M151"/>
+      <c r="K151" t="n">
+        <v>0.786069651741294</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0.416785714285714</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0.221293349629159</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
@@ -5751,13 +6201,13 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>0.178571428571429</v>
+        <v>0.107142857142857</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>0.414593220033038</v>
+        <v>0.292026812886269</v>
       </c>
       <c r="K152"/>
       <c r="L152"/>
@@ -5783,20 +6233,26 @@
         <v>79</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H153" t="n">
-        <v>0.178571428571429</v>
+        <v>0.107142857142857</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0.414593220033038</v>
-      </c>
-      <c r="K153"/>
-      <c r="L153"/>
-      <c r="M153"/>
+        <v>0.292026812886269</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0.736318407960199</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.343035714285714</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0.258691533206804</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
@@ -5853,7 +6309,7 @@
         <v>79</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H155" t="n">
         <v>0.107142857142857</v>
@@ -5864,9 +6320,15 @@
       <c r="J155" t="n">
         <v>0.320035633676683</v>
       </c>
-      <c r="K155"/>
-      <c r="L155"/>
-      <c r="M155"/>
+      <c r="K155" t="n">
+        <v>0.194029850746269</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0.0734821428571429</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0.187134745766301</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
@@ -5923,7 +6385,7 @@
         <v>79</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H157" t="n">
         <v>0.125</v>
@@ -5934,9 +6396,15 @@
       <c r="J157" t="n">
         <v>0.369995498067507</v>
       </c>
-      <c r="K157"/>
-      <c r="L157"/>
-      <c r="M157"/>
+      <c r="K157" t="n">
+        <v>0.169154228855721</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.0705357142857143</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0.181964796908967</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
@@ -5993,7 +6461,7 @@
         <v>79</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H159" t="n">
         <v>0.25</v>
@@ -6004,9 +6472,15 @@
       <c r="J159" t="n">
         <v>0.572678126609999</v>
       </c>
-      <c r="K159"/>
-      <c r="L159"/>
-      <c r="M159"/>
+      <c r="K159" t="n">
+        <v>0.343283582089552</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0.206875</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0.242525410416037</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
@@ -6063,7 +6537,7 @@
         <v>79</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H161" t="n">
         <v>0.482142857142857</v>
@@ -6074,9 +6548,15 @@
       <c r="J161" t="n">
         <v>0.816800718226758</v>
       </c>
-      <c r="K161"/>
-      <c r="L161"/>
-      <c r="M161"/>
+      <c r="K161" t="n">
+        <v>0.263681592039801</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0.311160714285714</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0.218179488468298</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
@@ -6133,7 +6613,7 @@
         <v>79</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -6144,9 +6624,15 @@
       <c r="J163" t="n">
         <v>0</v>
       </c>
-      <c r="K163"/>
-      <c r="L163"/>
-      <c r="M163"/>
+      <c r="K163" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0.0153571428571429</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0.0957217320393703</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
@@ -6203,7 +6689,7 @@
         <v>79</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H165" t="n">
         <v>0.678571428571429</v>
@@ -6214,9 +6700,15 @@
       <c r="J165" t="n">
         <v>0.977118003952216</v>
       </c>
-      <c r="K165"/>
-      <c r="L165"/>
-      <c r="M165"/>
+      <c r="K165" t="n">
+        <v>0.134328358208955</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0.403660714285714</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0.213505830614023</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
@@ -6241,13 +6733,13 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>0.232142857142857</v>
+        <v>0.321428571428571</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>0.0267166081862465</v>
       </c>
       <c r="J166" t="n">
-        <v>0.521461465326051</v>
+        <v>0.616140534670896</v>
       </c>
       <c r="K166"/>
       <c r="L166"/>
@@ -6273,20 +6765,26 @@
         <v>79</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H167" t="n">
-        <v>0.232142857142857</v>
+        <v>0.321428571428571</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>0.0267166081862465</v>
       </c>
       <c r="J167" t="n">
-        <v>0.521461465326051</v>
-      </c>
-      <c r="K167"/>
-      <c r="L167"/>
-      <c r="M167"/>
+        <v>0.616140534670896</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0.432835820895522</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0.314375</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0.25799254346659</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
@@ -6343,7 +6841,7 @@
         <v>79</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -6354,9 +6852,15 @@
       <c r="J169" t="n">
         <v>0</v>
       </c>
-      <c r="K169"/>
-      <c r="L169"/>
-      <c r="M169"/>
+      <c r="K169" t="n">
+        <v>1</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0.0682291666666667</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0.183994277183159</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
@@ -6413,7 +6917,7 @@
         <v>79</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -6424,9 +6928,15 @@
       <c r="J171" t="n">
         <v>0</v>
       </c>
-      <c r="K171"/>
-      <c r="L171"/>
-      <c r="M171"/>
+      <c r="K171" t="n">
+        <v>1</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0.0696875</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0.183182392514333</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
@@ -6483,7 +6993,7 @@
         <v>79</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -6494,9 +7004,15 @@
       <c r="J173" t="n">
         <v>0</v>
       </c>
-      <c r="K173"/>
-      <c r="L173"/>
-      <c r="M173"/>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0.157708333333333</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0.230712862909005</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
@@ -6553,7 +7069,7 @@
         <v>79</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H175" t="n">
         <v>0.416666666666667</v>
@@ -6564,9 +7080,15 @@
       <c r="J175" t="n">
         <v>0.76995026657195</v>
       </c>
-      <c r="K175"/>
-      <c r="L175"/>
-      <c r="M175"/>
+      <c r="K175" t="n">
+        <v>0.27363184079602</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.293333333333333</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0.210513715864978</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
@@ -6623,7 +7145,7 @@
         <v>79</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -6634,9 +7156,15 @@
       <c r="J177" t="n">
         <v>0</v>
       </c>
-      <c r="K177"/>
-      <c r="L177"/>
-      <c r="M177"/>
+      <c r="K177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0.0233333333333333</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0.111274656299454</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
@@ -6693,7 +7221,7 @@
         <v>79</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H179" t="n">
         <v>0.291666666666667</v>
@@ -6704,9 +7232,15 @@
       <c r="J179" t="n">
         <v>0.588370949257218</v>
       </c>
-      <c r="K179"/>
-      <c r="L179"/>
-      <c r="M179"/>
+      <c r="K179" t="n">
+        <v>0.716417910447761</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0.419375</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0.225006106840632</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
@@ -6731,13 +7265,13 @@
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>0</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>0</v>
+        <v>0.231364017823362</v>
       </c>
       <c r="K180"/>
       <c r="L180"/>
@@ -6763,20 +7297,26 @@
         <v>79</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181"/>
-      <c r="L181"/>
-      <c r="M181"/>
+        <v>0.231364017823362</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0.756218905472637</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0.3034375</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0.255987906608581</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
@@ -6833,7 +7373,7 @@
         <v>79</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -6844,9 +7384,15 @@
       <c r="J183" t="n">
         <v>0</v>
       </c>
-      <c r="K183"/>
-      <c r="L183"/>
-      <c r="M183"/>
+      <c r="K183" t="n">
+        <v>1</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0.1115625</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0.230688164317543</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
@@ -6903,7 +7449,7 @@
         <v>79</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -6914,9 +7460,15 @@
       <c r="J185" t="n">
         <v>0</v>
       </c>
-      <c r="K185"/>
-      <c r="L185"/>
-      <c r="M185"/>
+      <c r="K185" t="n">
+        <v>1</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0.107708333333333</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0.236442387153339</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
@@ -6973,7 +7525,7 @@
         <v>79</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H187" t="n">
         <v>0.104166666666667</v>
@@ -6984,9 +7536,15 @@
       <c r="J187" t="n">
         <v>0.312372804231433</v>
       </c>
-      <c r="K187"/>
-      <c r="L187"/>
-      <c r="M187"/>
+      <c r="K187" t="n">
+        <v>0.442786069651741</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0.177395833333333</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0.25204164851161</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
@@ -7043,7 +7601,7 @@
         <v>79</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H189" t="n">
         <v>0.25</v>
@@ -7054,9 +7612,15 @@
       <c r="J189" t="n">
         <v>0.53790383878476</v>
       </c>
-      <c r="K189"/>
-      <c r="L189"/>
-      <c r="M189"/>
+      <c r="K189" t="n">
+        <v>0.492537313432836</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0.297083333333333</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0.229240318604571</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
@@ -7113,7 +7677,7 @@
         <v>79</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -7124,9 +7688,15 @@
       <c r="J191" t="n">
         <v>0</v>
       </c>
-      <c r="K191"/>
-      <c r="L191"/>
-      <c r="M191"/>
+      <c r="K191" t="n">
+        <v>1</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0.0257291666666667</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0.125017054601498</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
@@ -7183,7 +7753,7 @@
         <v>79</v>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H193" t="n">
         <v>0.25</v>
@@ -7194,9 +7764,15 @@
       <c r="J193" t="n">
         <v>0.530529057727533</v>
       </c>
-      <c r="K193"/>
-      <c r="L193"/>
-      <c r="M193"/>
+      <c r="K193" t="n">
+        <v>0.716417910447761</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0.4228125</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0.257823542455937</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
@@ -7221,13 +7797,13 @@
         <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>0.254635630756703</v>
+        <v>0.309684029948097</v>
       </c>
       <c r="K194"/>
       <c r="L194"/>
@@ -7253,20 +7829,26 @@
         <v>79</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H195" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>0.254635630756703</v>
-      </c>
-      <c r="K195"/>
-      <c r="L195"/>
-      <c r="M195"/>
+        <v>0.309684029948097</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0.776119402985075</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0.351979166666667</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0.265225882122388</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
@@ -7323,7 +7905,7 @@
         <v>237</v>
       </c>
       <c r="G197" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -7334,9 +7916,15 @@
       <c r="J197" t="n">
         <v>0</v>
       </c>
-      <c r="K197"/>
-      <c r="L197"/>
-      <c r="M197"/>
+      <c r="K197" t="n">
+        <v>1</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0.0934375</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0.215607690033392</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
@@ -7393,7 +7981,7 @@
         <v>237</v>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H199" t="n">
         <v>0.125</v>
@@ -7404,9 +7992,15 @@
       <c r="J199" t="n">
         <v>0.369995498067507</v>
       </c>
-      <c r="K199"/>
-      <c r="L199"/>
-      <c r="M199"/>
+      <c r="K199" t="n">
+        <v>0.233830845771144</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0.0927083333333333</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0.211726451118641</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
@@ -7463,7 +8057,7 @@
         <v>237</v>
       </c>
       <c r="G201" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H201" t="n">
         <v>0.4375</v>
@@ -7474,9 +8068,15 @@
       <c r="J201" t="n">
         <v>0.786032211267904</v>
       </c>
-      <c r="K201"/>
-      <c r="L201"/>
-      <c r="M201"/>
+      <c r="K201" t="n">
+        <v>0.199004975124378</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0.197395833333333</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0.263224498552189</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
@@ -7533,7 +8133,7 @@
         <v>237</v>
       </c>
       <c r="G203" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H203" t="n">
         <v>0.333333333333333</v>
@@ -7544,9 +8144,15 @@
       <c r="J203" t="n">
         <v>0.643230849485614</v>
       </c>
-      <c r="K203"/>
-      <c r="L203"/>
-      <c r="M203"/>
+      <c r="K203" t="n">
+        <v>0.393034825870647</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0.298020833333333</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0.213485266993297</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
@@ -7603,7 +8209,7 @@
         <v>237</v>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -7614,9 +8220,15 @@
       <c r="J205" t="n">
         <v>0</v>
       </c>
-      <c r="K205"/>
-      <c r="L205"/>
-      <c r="M205"/>
+      <c r="K205" t="n">
+        <v>1</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0.0167708333333333</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0.0926930108448954</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
@@ -7673,7 +8285,7 @@
         <v>237</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H207" t="n">
         <v>0.729166666666667</v>
@@ -7684,9 +8296,15 @@
       <c r="J207" t="n">
         <v>1</v>
       </c>
-      <c r="K207"/>
-      <c r="L207"/>
-      <c r="M207"/>
+      <c r="K207" t="n">
+        <v>0.134328358208955</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0.441979166666667</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0.241947700012745</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
@@ -7743,7 +8361,7 @@
         <v>237</v>
       </c>
       <c r="G209" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -7754,9 +8372,15 @@
       <c r="J209" t="n">
         <v>0</v>
       </c>
-      <c r="K209"/>
-      <c r="L209"/>
-      <c r="M209"/>
+      <c r="K209" t="n">
+        <v>1</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.314895833333333</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0.265404926158137</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
@@ -7813,7 +8437,7 @@
         <v>1900</v>
       </c>
       <c r="G211" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -7824,9 +8448,15 @@
       <c r="J211" t="n">
         <v>0</v>
       </c>
-      <c r="K211"/>
-      <c r="L211"/>
-      <c r="M211"/>
+      <c r="K211" t="n">
+        <v>1</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0.104196428571429</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0.207776661588622</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
@@ -7883,7 +8513,7 @@
         <v>1900</v>
       </c>
       <c r="G213" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -7894,9 +8524,15 @@
       <c r="J213" t="n">
         <v>0</v>
       </c>
-      <c r="K213"/>
-      <c r="L213"/>
-      <c r="M213"/>
+      <c r="K213" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.113214285714286</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0.213674949161307</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
@@ -7953,7 +8589,7 @@
         <v>1900</v>
       </c>
       <c r="G215" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H215" t="n">
         <v>0.285714285714286</v>
@@ -7964,9 +8600,15 @@
       <c r="J215" t="n">
         <v>0.584065413234268</v>
       </c>
-      <c r="K215"/>
-      <c r="L215"/>
-      <c r="M215"/>
+      <c r="K215" t="n">
+        <v>0.373134328358209</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0.246339285714286</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0.237256934949697</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
@@ -8023,7 +8665,7 @@
         <v>1900</v>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H217" t="n">
         <v>0.428571428571428</v>
@@ -8034,9 +8676,15 @@
       <c r="J217" t="n">
         <v>0.760780114004445</v>
       </c>
-      <c r="K217"/>
-      <c r="L217"/>
-      <c r="M217"/>
+      <c r="K217" t="n">
+        <v>0.243781094527363</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0.276964285714286</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0.19340731063323</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
@@ -8093,7 +8741,7 @@
         <v>1900</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -8104,9 +8752,15 @@
       <c r="J219" t="n">
         <v>0</v>
       </c>
-      <c r="K219"/>
-      <c r="L219"/>
-      <c r="M219"/>
+      <c r="K219" t="n">
+        <v>1</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0.00205357142857143</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0.0266238528978017</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
@@ -8163,7 +8817,7 @@
         <v>1900</v>
       </c>
       <c r="G221" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H221" t="n">
         <v>0.410714285714286</v>
@@ -8174,9 +8828,15 @@
       <c r="J221" t="n">
         <v>0.757274409410401</v>
       </c>
-      <c r="K221"/>
-      <c r="L221"/>
-      <c r="M221"/>
+      <c r="K221" t="n">
+        <v>0.552238805970149</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0.434821428571429</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0.237035321776882</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
@@ -8201,13 +8861,13 @@
         <v>0</v>
       </c>
       <c r="H222" t="n">
-        <v>0.178571428571429</v>
+        <v>0.375</v>
       </c>
       <c r="I222" t="n">
-        <v>0</v>
+        <v>0.0351533355176331</v>
       </c>
       <c r="J222" t="n">
-        <v>0.436103101473066</v>
+        <v>0.714846664482367</v>
       </c>
       <c r="K222"/>
       <c r="L222"/>
@@ -8233,20 +8893,26 @@
         <v>1900</v>
       </c>
       <c r="G223" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H223" t="n">
-        <v>0.178571428571429</v>
+        <v>0.375</v>
       </c>
       <c r="I223" t="n">
-        <v>0</v>
+        <v>0.0351533355176331</v>
       </c>
       <c r="J223" t="n">
-        <v>0.436103101473066</v>
-      </c>
-      <c r="K223"/>
-      <c r="L223"/>
-      <c r="M223"/>
+        <v>0.714846664482367</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0.398009950248756</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0.234814340130321</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
@@ -8303,7 +8969,7 @@
         <v>1898</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -8314,9 +8980,15 @@
       <c r="J225" t="n">
         <v>0</v>
       </c>
-      <c r="K225"/>
-      <c r="L225"/>
-      <c r="M225"/>
+      <c r="K225" t="n">
+        <v>1</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0.233874073703196</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
@@ -8373,7 +9045,7 @@
         <v>1898</v>
       </c>
       <c r="G227" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -8384,9 +9056,15 @@
       <c r="J227" t="n">
         <v>0</v>
       </c>
-      <c r="K227"/>
-      <c r="L227"/>
-      <c r="M227"/>
+      <c r="K227" t="n">
+        <v>1</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0.105625</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0.235543575607896</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
@@ -8443,7 +9121,7 @@
         <v>1898</v>
       </c>
       <c r="G229" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -8454,9 +9132,15 @@
       <c r="J229" t="n">
         <v>0</v>
       </c>
-      <c r="K229"/>
-      <c r="L229"/>
-      <c r="M229"/>
+      <c r="K229" t="n">
+        <v>1</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0.306919642857143</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0.253280126088554</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
@@ -8513,7 +9197,7 @@
         <v>1898</v>
       </c>
       <c r="G231" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -8524,9 +9208,15 @@
       <c r="J231" t="n">
         <v>0</v>
       </c>
-      <c r="K231"/>
-      <c r="L231"/>
-      <c r="M231"/>
+      <c r="K231" t="n">
+        <v>1</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0.344821428571429</v>
+      </c>
+      <c r="M231" t="n">
+        <v>0.223648285907024</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
@@ -8583,7 +9273,7 @@
         <v>1898</v>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -8594,9 +9284,15 @@
       <c r="J233" t="n">
         <v>0</v>
       </c>
-      <c r="K233"/>
-      <c r="L233"/>
-      <c r="M233"/>
+      <c r="K233" t="n">
+        <v>1</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0.035625</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0.142402109792109</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
@@ -8653,7 +9349,7 @@
         <v>1898</v>
       </c>
       <c r="G235" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -8664,9 +9360,15 @@
       <c r="J235" t="n">
         <v>0</v>
       </c>
-      <c r="K235"/>
-      <c r="L235"/>
-      <c r="M235"/>
+      <c r="K235" t="n">
+        <v>1</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0.456964285714286</v>
+      </c>
+      <c r="M235" t="n">
+        <v>0.244190721676662</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
@@ -8691,13 +9393,13 @@
         <v>0</v>
       </c>
       <c r="H236" t="n">
-        <v>0.357142857142857</v>
+        <v>0.571428571428571</v>
       </c>
       <c r="I236" t="n">
-        <v>0.0588895015827412</v>
+        <v>0.257919314093205</v>
       </c>
       <c r="J236" t="n">
-        <v>0.655396212702973</v>
+        <v>0.884937828763938</v>
       </c>
       <c r="K236"/>
       <c r="L236"/>
@@ -8723,20 +9425,26 @@
         <v>1898</v>
       </c>
       <c r="G237" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H237" t="n">
-        <v>0.357142857142857</v>
+        <v>0.571428571428571</v>
       </c>
       <c r="I237" t="n">
-        <v>0.0588895015827412</v>
+        <v>0.257919314093205</v>
       </c>
       <c r="J237" t="n">
-        <v>0.655396212702973</v>
-      </c>
-      <c r="K237"/>
-      <c r="L237"/>
-      <c r="M237"/>
+        <v>0.884937828763938</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0.199004975124378</v>
+      </c>
+      <c r="L237" t="n">
+        <v>0.332767857142857</v>
+      </c>
+      <c r="M237" t="n">
+        <v>0.255215426742345</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
@@ -8793,7 +9501,7 @@
         <v>1899</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -8804,9 +9512,15 @@
       <c r="J239" t="n">
         <v>0</v>
       </c>
-      <c r="K239"/>
-      <c r="L239"/>
-      <c r="M239"/>
+      <c r="K239" t="n">
+        <v>1</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0.0926785714285714</v>
+      </c>
+      <c r="M239" t="n">
+        <v>0.205048810320581</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
@@ -8863,7 +9577,7 @@
         <v>1899</v>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -8874,9 +9588,15 @@
       <c r="J241" t="n">
         <v>0</v>
       </c>
-      <c r="K241"/>
-      <c r="L241"/>
-      <c r="M241"/>
+      <c r="K241" t="n">
+        <v>1</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="M241" t="n">
+        <v>0.188910659324561</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
@@ -8933,7 +9653,7 @@
         <v>1899</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H243" t="n">
         <v>0.107142857142857</v>
@@ -8944,9 +9664,15 @@
       <c r="J243" t="n">
         <v>0.320035633676683</v>
       </c>
-      <c r="K243"/>
-      <c r="L243"/>
-      <c r="M243"/>
+      <c r="K243" t="n">
+        <v>0.736318407960199</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0.261428571428571</v>
+      </c>
+      <c r="M243" t="n">
+        <v>0.241543998539475</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
@@ -9003,7 +9729,7 @@
         <v>1899</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H245" t="n">
         <v>0.303571428571429</v>
@@ -9014,9 +9740,15 @@
       <c r="J245" t="n">
         <v>0.596596190418204</v>
       </c>
-      <c r="K245"/>
-      <c r="L245"/>
-      <c r="M245"/>
+      <c r="K245" t="n">
+        <v>0.427860696517413</v>
+      </c>
+      <c r="L245" t="n">
+        <v>0.289285714285714</v>
+      </c>
+      <c r="M245" t="n">
+        <v>0.211690130891281</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
@@ -9073,7 +9805,7 @@
         <v>1899</v>
       </c>
       <c r="G247" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -9084,9 +9816,15 @@
       <c r="J247" t="n">
         <v>0</v>
       </c>
-      <c r="K247"/>
-      <c r="L247"/>
-      <c r="M247"/>
+      <c r="K247" t="n">
+        <v>1</v>
+      </c>
+      <c r="L247" t="n">
+        <v>0.0246428571428571</v>
+      </c>
+      <c r="M247" t="n">
+        <v>0.127990331555934</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
@@ -9143,7 +9881,7 @@
         <v>1899</v>
       </c>
       <c r="G249" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H249" t="n">
         <v>0.535714285714286</v>
@@ -9154,9 +9892,15 @@
       <c r="J249" t="n">
         <v>0.891493263984734</v>
       </c>
-      <c r="K249"/>
-      <c r="L249"/>
-      <c r="M249"/>
+      <c r="K249" t="n">
+        <v>0.353233830845771</v>
+      </c>
+      <c r="L249" t="n">
+        <v>0.428035714285714</v>
+      </c>
+      <c r="M249" t="n">
+        <v>0.237414669534603</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
@@ -9181,13 +9925,13 @@
         <v>0</v>
       </c>
       <c r="H250" t="n">
-        <v>0.196428571428571</v>
+        <v>0.303571428571429</v>
       </c>
       <c r="I250" t="n">
         <v>0</v>
       </c>
       <c r="J250" t="n">
-        <v>0.454864660363769</v>
+        <v>0.614183385131584</v>
       </c>
       <c r="K250"/>
       <c r="L250"/>
@@ -9213,20 +9957,26 @@
         <v>1899</v>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H251" t="n">
-        <v>0.196428571428571</v>
+        <v>0.303571428571429</v>
       </c>
       <c r="I251" t="n">
         <v>0</v>
       </c>
       <c r="J251" t="n">
-        <v>0.454864660363769</v>
-      </c>
-      <c r="K251"/>
-      <c r="L251"/>
-      <c r="M251"/>
+        <v>0.614183385131584</v>
+      </c>
+      <c r="K251" t="n">
+        <v>0.527363184079602</v>
+      </c>
+      <c r="L251" t="n">
+        <v>0.351696428571429</v>
+      </c>
+      <c r="M251" t="n">
+        <v>0.267795503197241</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
@@ -9283,7 +10033,7 @@
         <v>1899</v>
       </c>
       <c r="G253" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -9294,9 +10044,15 @@
       <c r="J253" t="n">
         <v>0</v>
       </c>
-      <c r="K253"/>
-      <c r="L253"/>
-      <c r="M253"/>
+      <c r="K253" t="n">
+        <v>1</v>
+      </c>
+      <c r="L253" t="n">
+        <v>0.0916964285714286</v>
+      </c>
+      <c r="M253" t="n">
+        <v>0.201487882058065</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
@@ -9353,7 +10109,7 @@
         <v>1899</v>
       </c>
       <c r="G255" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -9364,9 +10120,15 @@
       <c r="J255" t="n">
         <v>0</v>
       </c>
-      <c r="K255"/>
-      <c r="L255"/>
-      <c r="M255"/>
+      <c r="K255" t="n">
+        <v>1</v>
+      </c>
+      <c r="L255" t="n">
+        <v>0.0959821428571429</v>
+      </c>
+      <c r="M255" t="n">
+        <v>0.210113101254876</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
@@ -9423,7 +10185,7 @@
         <v>1899</v>
       </c>
       <c r="G257" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H257" t="n">
         <v>0.482142857142857</v>
@@ -9434,9 +10196,15 @@
       <c r="J257" t="n">
         <v>0.811087163466639</v>
       </c>
-      <c r="K257"/>
-      <c r="L257"/>
-      <c r="M257"/>
+      <c r="K257" t="n">
+        <v>0.218905472636816</v>
+      </c>
+      <c r="L257" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="M257" t="n">
+        <v>0.24394333708367</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
@@ -9493,7 +10261,7 @@
         <v>1899</v>
       </c>
       <c r="G259" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H259" t="n">
         <v>0.357142857142857</v>
@@ -9504,9 +10272,15 @@
       <c r="J259" t="n">
         <v>0.665303816106125</v>
       </c>
-      <c r="K259"/>
-      <c r="L259"/>
-      <c r="M259"/>
+      <c r="K259" t="n">
+        <v>0.358208955223881</v>
+      </c>
+      <c r="L259" t="n">
+        <v>0.277678571428571</v>
+      </c>
+      <c r="M259" t="n">
+        <v>0.215841074043334</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
@@ -9563,7 +10337,7 @@
         <v>1899</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -9574,9 +10348,15 @@
       <c r="J261" t="n">
         <v>0</v>
       </c>
-      <c r="K261"/>
-      <c r="L261"/>
-      <c r="M261"/>
+      <c r="K261" t="n">
+        <v>1</v>
+      </c>
+      <c r="L261" t="n">
+        <v>0.0140178571428572</v>
+      </c>
+      <c r="M261" t="n">
+        <v>0.10120349123823</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
@@ -9633,7 +10413,7 @@
         <v>1899</v>
       </c>
       <c r="G263" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H263" t="n">
         <v>0.464285714285714</v>
@@ -9644,9 +10424,15 @@
       <c r="J263" t="n">
         <v>0.781034267668553</v>
       </c>
-      <c r="K263"/>
-      <c r="L263"/>
-      <c r="M263"/>
+      <c r="K263" t="n">
+        <v>0.383084577114428</v>
+      </c>
+      <c r="L263" t="n">
+        <v>0.401696428571429</v>
+      </c>
+      <c r="M263" t="n">
+        <v>0.238975980416396</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
@@ -9671,13 +10457,13 @@
         <v>0</v>
       </c>
       <c r="H264" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="I264" t="n">
         <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>0.422851997791436</v>
+        <v>0</v>
       </c>
       <c r="K264"/>
       <c r="L264"/>
@@ -9703,20 +10489,26 @@
         <v>1899</v>
       </c>
       <c r="G265" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H265" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="I265" t="n">
         <v>0</v>
       </c>
       <c r="J265" t="n">
-        <v>0.422851997791436</v>
-      </c>
-      <c r="K265"/>
-      <c r="L265"/>
-      <c r="M265"/>
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>1</v>
+      </c>
+      <c r="L265" t="n">
+        <v>0.330178571428571</v>
+      </c>
+      <c r="M265" t="n">
+        <v>0.249897361250336</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
@@ -9773,7 +10565,7 @@
         <v>1900</v>
       </c>
       <c r="G267" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -9784,9 +10576,15 @@
       <c r="J267" t="n">
         <v>0</v>
       </c>
-      <c r="K267"/>
-      <c r="L267"/>
-      <c r="M267"/>
+      <c r="K267" t="n">
+        <v>1</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0.0917708333333333</v>
+      </c>
+      <c r="M267" t="n">
+        <v>0.203386597107985</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
@@ -9843,7 +10641,7 @@
         <v>1900</v>
       </c>
       <c r="G269" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -9854,9 +10652,15 @@
       <c r="J269" t="n">
         <v>0</v>
       </c>
-      <c r="K269"/>
-      <c r="L269"/>
-      <c r="M269"/>
+      <c r="K269" t="n">
+        <v>1</v>
+      </c>
+      <c r="L269" t="n">
+        <v>0.104479166666667</v>
+      </c>
+      <c r="M269" t="n">
+        <v>0.224162836104277</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
@@ -9913,7 +10717,7 @@
         <v>1900</v>
       </c>
       <c r="G271" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -9924,9 +10728,15 @@
       <c r="J271" t="n">
         <v>0</v>
       </c>
-      <c r="K271"/>
-      <c r="L271"/>
-      <c r="M271"/>
+      <c r="K271" t="n">
+        <v>1</v>
+      </c>
+      <c r="L271" t="n">
+        <v>0.180572916666667</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0.252435869807093</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
@@ -9983,7 +10793,7 @@
         <v>1900</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H273" t="n">
         <v>0.0416666666666667</v>
@@ -9994,9 +10804,15 @@
       <c r="J273" t="n">
         <v>0.138294194204506</v>
       </c>
-      <c r="K273"/>
-      <c r="L273"/>
-      <c r="M273"/>
+      <c r="K273" t="n">
+        <v>0.890547263681592</v>
+      </c>
+      <c r="L273" t="n">
+        <v>0.274895833333333</v>
+      </c>
+      <c r="M273" t="n">
+        <v>0.198882116936255</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
@@ -10053,7 +10869,7 @@
         <v>1900</v>
       </c>
       <c r="G275" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -10064,9 +10880,15 @@
       <c r="J275" t="n">
         <v>0</v>
       </c>
-      <c r="K275"/>
-      <c r="L275"/>
-      <c r="M275"/>
+      <c r="K275" t="n">
+        <v>1</v>
+      </c>
+      <c r="L275" t="n">
+        <v>0.0189583333333333</v>
+      </c>
+      <c r="M275" t="n">
+        <v>0.0872006224877765</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
@@ -10123,7 +10945,7 @@
         <v>1900</v>
       </c>
       <c r="G277" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H277" t="n">
         <v>0.229166666666667</v>
@@ -10134,9 +10956,15 @@
       <c r="J277" t="n">
         <v>0.49630040275005</v>
       </c>
-      <c r="K277"/>
-      <c r="L277"/>
-      <c r="M277"/>
+      <c r="K277" t="n">
+        <v>0.711442786069652</v>
+      </c>
+      <c r="L277" t="n">
+        <v>0.420729166666667</v>
+      </c>
+      <c r="M277" t="n">
+        <v>0.256125213893384</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
@@ -10161,13 +10989,13 @@
         <v>0</v>
       </c>
       <c r="H278" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0302749192283137</v>
+        <v>0.109529486156929</v>
       </c>
       <c r="J278" t="n">
-        <v>0.636391747438353</v>
+        <v>0.76547051384307</v>
       </c>
       <c r="K278"/>
       <c r="L278"/>
@@ -10193,20 +11021,26 @@
         <v>1900</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H279" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="I279" t="n">
-        <v>0.0302749192283137</v>
+        <v>0.109529486156929</v>
       </c>
       <c r="J279" t="n">
-        <v>0.636391747438353</v>
-      </c>
-      <c r="K279"/>
-      <c r="L279"/>
-      <c r="M279"/>
+        <v>0.76547051384307</v>
+      </c>
+      <c r="K279" t="n">
+        <v>0.36318407960199</v>
+      </c>
+      <c r="L279" t="n">
+        <v>0.340208333333333</v>
+      </c>
+      <c r="M279" t="n">
+        <v>0.265601525796266</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
@@ -10263,7 +11097,7 @@
         <v>1899</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -10274,9 +11108,15 @@
       <c r="J281" t="n">
         <v>0</v>
       </c>
-      <c r="K281"/>
-      <c r="L281"/>
-      <c r="M281"/>
+      <c r="K281" t="n">
+        <v>1</v>
+      </c>
+      <c r="L281" t="n">
+        <v>0.0548958333333333</v>
+      </c>
+      <c r="M281" t="n">
+        <v>0.163378064873891</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
@@ -10333,7 +11173,7 @@
         <v>1899</v>
       </c>
       <c r="G283" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -10344,9 +11184,15 @@
       <c r="J283" t="n">
         <v>0</v>
       </c>
-      <c r="K283"/>
-      <c r="L283"/>
-      <c r="M283"/>
+      <c r="K283" t="n">
+        <v>1</v>
+      </c>
+      <c r="L283" t="n">
+        <v>0.0726041666666667</v>
+      </c>
+      <c r="M283" t="n">
+        <v>0.192510268195109</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
@@ -10403,7 +11249,7 @@
         <v>1899</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -10414,9 +11260,15 @@
       <c r="J285" t="n">
         <v>0</v>
       </c>
-      <c r="K285"/>
-      <c r="L285"/>
-      <c r="M285"/>
+      <c r="K285" t="n">
+        <v>1</v>
+      </c>
+      <c r="L285" t="n">
+        <v>0.181041666666667</v>
+      </c>
+      <c r="M285" t="n">
+        <v>0.245700305403508</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
@@ -10473,7 +11325,7 @@
         <v>1899</v>
       </c>
       <c r="G287" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H287" t="n">
         <v>0.1875</v>
@@ -10484,9 +11336,15 @@
       <c r="J287" t="n">
         <v>0.456411092588118</v>
       </c>
-      <c r="K287"/>
-      <c r="L287"/>
-      <c r="M287"/>
+      <c r="K287" t="n">
+        <v>0.532338308457711</v>
+      </c>
+      <c r="L287" t="n">
+        <v>0.262604166666667</v>
+      </c>
+      <c r="M287" t="n">
+        <v>0.215809102678398</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
@@ -10543,7 +11401,7 @@
         <v>1899</v>
       </c>
       <c r="G289" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -10554,9 +11412,15 @@
       <c r="J289" t="n">
         <v>0</v>
       </c>
-      <c r="K289"/>
-      <c r="L289"/>
-      <c r="M289"/>
+      <c r="K289" t="n">
+        <v>1</v>
+      </c>
+      <c r="L289" t="n">
+        <v>0.0157291666666667</v>
+      </c>
+      <c r="M289" t="n">
+        <v>0.115919807854461</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
@@ -10613,7 +11477,7 @@
         <v>1899</v>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H291" t="n">
         <v>0.166666666666667</v>
@@ -10624,9 +11488,15 @@
       <c r="J291" t="n">
         <v>0.424175688469012</v>
       </c>
-      <c r="K291"/>
-      <c r="L291"/>
-      <c r="M291"/>
+      <c r="K291" t="n">
+        <v>0.840796019900497</v>
+      </c>
+      <c r="L291" t="n">
+        <v>0.415104166666667</v>
+      </c>
+      <c r="M291" t="n">
+        <v>0.244637645779246</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
@@ -10651,13 +11521,13 @@
         <v>0</v>
       </c>
       <c r="H292" t="n">
-        <v>0.541666666666667</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="I292" t="n">
-        <v>0.166412912013105</v>
+        <v>0.241842902721225</v>
       </c>
       <c r="J292" t="n">
-        <v>0.916920421320228</v>
+        <v>0.924823763945441</v>
       </c>
       <c r="K292"/>
       <c r="L292"/>
@@ -10683,20 +11553,26 @@
         <v>1899</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H293" t="n">
-        <v>0.541666666666667</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="I293" t="n">
-        <v>0.166412912013105</v>
+        <v>0.241842902721225</v>
       </c>
       <c r="J293" t="n">
-        <v>0.916920421320228</v>
-      </c>
-      <c r="K293"/>
-      <c r="L293"/>
-      <c r="M293"/>
+        <v>0.924823763945441</v>
+      </c>
+      <c r="K293" t="n">
+        <v>0.18407960199005</v>
+      </c>
+      <c r="L293" t="n">
+        <v>0.320833333333333</v>
+      </c>
+      <c r="M293" t="n">
+        <v>0.269594350650839</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
@@ -10753,7 +11629,7 @@
         <v>5696</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -10764,9 +11640,15 @@
       <c r="J295" t="n">
         <v>0</v>
       </c>
-      <c r="K295"/>
-      <c r="L295"/>
-      <c r="M295"/>
+      <c r="K295" t="n">
+        <v>1</v>
+      </c>
+      <c r="L295" t="n">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="M295" t="n">
+        <v>0.137226582121946</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
@@ -10823,7 +11705,7 @@
         <v>5696</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -10834,9 +11716,15 @@
       <c r="J297" t="n">
         <v>0</v>
       </c>
-      <c r="K297"/>
-      <c r="L297"/>
-      <c r="M297"/>
+      <c r="K297" t="n">
+        <v>1</v>
+      </c>
+      <c r="L297" t="n">
+        <v>0.0594791666666667</v>
+      </c>
+      <c r="M297" t="n">
+        <v>0.162537811550287</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
@@ -10893,7 +11781,7 @@
         <v>5696</v>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H299" t="n">
         <v>0.125</v>
@@ -10904,9 +11792,15 @@
       <c r="J299" t="n">
         <v>0.369995498067507</v>
       </c>
-      <c r="K299"/>
-      <c r="L299"/>
-      <c r="M299"/>
+      <c r="K299" t="n">
+        <v>0.437810945273632</v>
+      </c>
+      <c r="L299" t="n">
+        <v>0.1609375</v>
+      </c>
+      <c r="M299" t="n">
+        <v>0.230934228587746</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
@@ -10963,7 +11857,7 @@
         <v>5696</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H301" t="n">
         <v>0.229166666666667</v>
@@ -10974,9 +11868,15 @@
       <c r="J301" t="n">
         <v>0.495228289784367</v>
       </c>
-      <c r="K301"/>
-      <c r="L301"/>
-      <c r="M301"/>
+      <c r="K301" t="n">
+        <v>0.447761194029851</v>
+      </c>
+      <c r="L301" t="n">
+        <v>0.229791666666667</v>
+      </c>
+      <c r="M301" t="n">
+        <v>0.192611442322537</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
@@ -11033,7 +11933,7 @@
         <v>5696</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -11044,9 +11944,15 @@
       <c r="J303" t="n">
         <v>0</v>
       </c>
-      <c r="K303"/>
-      <c r="L303"/>
-      <c r="M303"/>
+      <c r="K303" t="n">
+        <v>1</v>
+      </c>
+      <c r="L303" t="n">
+        <v>0.00843750000000001</v>
+      </c>
+      <c r="M303" t="n">
+        <v>0.0739922024154292</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
@@ -11103,7 +12009,7 @@
         <v>5696</v>
       </c>
       <c r="G305" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H305" t="n">
         <v>0.270833333333333</v>
@@ -11114,9 +12020,15 @@
       <c r="J305" t="n">
         <v>0.551871364671475</v>
       </c>
-      <c r="K305"/>
-      <c r="L305"/>
-      <c r="M305"/>
+      <c r="K305" t="n">
+        <v>0.656716417910448</v>
+      </c>
+      <c r="L305" t="n">
+        <v>0.4046875</v>
+      </c>
+      <c r="M305" t="n">
+        <v>0.249995092602589</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
@@ -11141,13 +12053,13 @@
         <v>0</v>
       </c>
       <c r="H306" t="n">
-        <v>0.229166666666667</v>
+        <v>0.270833333333333</v>
       </c>
       <c r="I306" t="n">
         <v>0</v>
       </c>
       <c r="J306" t="n">
-        <v>0.49630040275005</v>
+        <v>0.558240357530865</v>
       </c>
       <c r="K306"/>
       <c r="L306"/>
@@ -11173,20 +12085,26 @@
         <v>5696</v>
       </c>
       <c r="G307" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H307" t="n">
-        <v>0.229166666666667</v>
+        <v>0.270833333333333</v>
       </c>
       <c r="I307" t="n">
         <v>0</v>
       </c>
       <c r="J307" t="n">
-        <v>0.49630040275005</v>
-      </c>
-      <c r="K307"/>
-      <c r="L307"/>
-      <c r="M307"/>
+        <v>0.558240357530865</v>
+      </c>
+      <c r="K307" t="n">
+        <v>0.567164179104478</v>
+      </c>
+      <c r="L307" t="n">
+        <v>0.3546875</v>
+      </c>
+      <c r="M307" t="n">
+        <v>0.254517029811066</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
